--- a/data/content_plan.xlsx
+++ b/data/content_plan.xlsx
@@ -9863,7 +9863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9933,82 +9933,70 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Запрещено на макете</t>
+          <t>Стиль</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Цены, слова «скидка», «дешевле», «акция», знаки %, зачёркнутая цена (цены меняются, а Авито уже отклонял объявления за такие первые фото). Логотипы автопроизводителей (VW, Audi, Škoda, Seat и др.) не использовать — только названия коробок и артикулы текстом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
+          <t>Единый для всех постов: тёмный технический фон или светлый студийный фон, один акцентный цвет, шрифт без засечек. Логотип Leo.Parts в одном и том же месте. Утвердить 1–2 шаблона (одиночный пост и карусель), затем делать серию по шаблону.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Стиль</t>
+          <t>Структура одиночного поста</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Единый для всех постов: тёмный технический фон или светлый студийный фон, один акцентный цвет, шрифт без засечек. Логотип Leo.Parts в одном и том же месте. Утвердить 1–2 шаблона (одиночный пост и карусель), затем делать серию по шаблону.</t>
+          <t>Вверху — заголовок (до 6 слов), под ним подзаголовок. В центре — фото товара. Слева или снизу — 3 пункта. Внизу — плашка с артикулом.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Структура одиночного поста</t>
+          <t>Структура карусели</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Вверху — заголовок (до 6 слов), под ним подзаголовок. В центре — фото товара. Слева или снизу — 3 пункта. Внизу — плашка с артикулом.</t>
+          <t>Слайд 1: обложка с заголовком. Дальше — по слайду на вариант товара (см. колонку «Состав слайдов»). Последний слайд: «Где купить: Ozon · WB · Авито · сайт» без цен.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Структура карусели</t>
+          <t>Образовательные посты</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Слайд 1: обложка с заголовком. Дальше — по слайду на вариант товара (см. колонку «Состав слайдов»). Последний слайд: «Где купить: Ozon · WB · Авито · сайт» без цен.</t>
+          <t>Строки с голубой заливкой — полезные и брендовые посты. Им нужны схемы и иконки; текст слайдов в колонке «Состав слайдов». Выделены в плане каждый понедельник.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Образовательные посты</t>
+          <t>Согласование</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Строки с голубой заливкой — полезные и брендовые посты. Им нужны схемы и иконки; текст слайдов в колонке «Состав слайдов». Выделены в плане каждый понедельник.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t>Менять статус в колонке «Статус дизайна»: не начато → в работе → на согласовании → правки → готово. Публикацию отмечать в последней колонке.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Согласование</t>
+          <t>Открытые вопросы к владельцу</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Менять статус в колонке «Статус дизайна»: не начато → в работе → на согласовании → правки → готово. Публикацию отмечать в последней колонке.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Открытые вопросы к владельцу</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>1) Сроки отправки и условия возврата для поста «Отправка и оплата» (там стоят плейсхолдеры в квадратных скобках). 2) Остаток для позиций с предупреждением в колонке «Предупреждение». 3) Фото для карточек, где написано «НЕТ ФОТО». 4) Можно ли в постах писать, что на сайте и Авито цены ниже, чем на маркетплейсах.</t>
         </is>

--- a/data/content_plan.xlsx
+++ b/data/content_plan.xlsx
@@ -20,9 +20,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="DD.MM.YYYY"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -102,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,7 +109,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,7 +118,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -134,6 +133,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,7 +630,7 @@
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="12" t="n">
         <v>46321</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -685,7 +690,7 @@
       <c r="M2" s="4" t="inlineStr">
         <is>
           <t>Привет! Мы — Leo.Parts 👋
-Продаём запчасти для коробок DSG: мехатроники, ремкомплекты, гидроплиты, штоки, сальники, фильтры, соленоиды и многое другое. В основном DSG7 DQ200, а также DQ250, DQ500 и вариаторы.
+Продаём запчасти для коробок DSG: мехатроники, ремкомплекты, гидроплиты, штоки, сальники, фильтры, соленоиды и многое другое. В основном DSG7 DQ200, а также DQ250, DQ500, 0B5 и вариаторы.
 📦 Новые детали и оригинал VAG
 🔧 Для автосервисов и частных мастеров
 🛒 Ozon, Wildberries, Авито и сайт — ссылки в шапке профиля
@@ -695,7 +700,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dsg #дсг #роботдсг #мехатроник #dq250 #golf #skoda #запчастидляакпп #автозапчасти</t>
+          <t>#leoparts #dsg #дсг #роботдсг #мехатроник #dq250 #golf #skoda #запчастидляакпп #автозапчасти #0b5</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
@@ -716,7 +721,7 @@
       <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="13" t="n">
         <v>46322</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -813,7 +818,7 @@
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="13" t="n">
         <v>46323</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -910,7 +915,7 @@
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="13" t="n">
         <v>46324</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1007,7 +1012,7 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="13" t="n">
         <v>46325</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1104,7 +1109,7 @@
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="12" t="n">
         <v>46328</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1194,7 +1199,7 @@
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="13" t="n">
         <v>46329</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1291,7 +1296,7 @@
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="13" t="n">
         <v>46330</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1388,7 +1393,7 @@
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="13" t="n">
         <v>46331</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1489,7 +1494,7 @@
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="13" t="n">
         <v>46332</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1586,7 +1591,7 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="12" t="n">
         <v>46335</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1676,7 +1681,7 @@
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="13" t="n">
         <v>46336</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1773,7 +1778,7 @@
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="13" t="n">
         <v>46337</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1870,7 +1875,7 @@
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="13" t="n">
         <v>46338</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1973,7 +1978,7 @@
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="13" t="n">
         <v>46339</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -2076,7 +2081,7 @@
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="12" t="n">
         <v>46342</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2166,7 +2171,7 @@
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="13" t="n">
         <v>46343</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2267,7 +2272,7 @@
       <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="13" t="n">
         <v>46344</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2370,7 +2375,7 @@
       <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="13" t="n">
         <v>46345</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2467,7 +2472,7 @@
       <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="13" t="n">
         <v>46346</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2564,7 +2569,7 @@
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="12" t="n">
         <v>46349</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2652,7 +2657,7 @@
       <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="13" t="n">
         <v>46350</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2753,7 +2758,7 @@
       <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="13" t="n">
         <v>46351</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -2850,7 +2855,7 @@
       <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="13" t="n">
         <v>46352</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -2947,7 +2952,7 @@
       <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="13" t="n">
         <v>46353</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -3044,7 +3049,7 @@
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="12" t="n">
         <v>46356</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3134,7 +3139,7 @@
       <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="13" t="n">
         <v>46357</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -3231,7 +3236,7 @@
       <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="13" t="n">
         <v>46358</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3338,7 +3343,7 @@
       <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="13" t="n">
         <v>46359</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -3435,7 +3440,7 @@
       <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="13" t="n">
         <v>46360</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3536,7 +3541,7 @@
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="12" t="n">
         <v>46363</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3626,7 +3631,7 @@
       <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="13" t="n">
         <v>46364</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -3723,7 +3728,7 @@
       <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="13" t="n">
         <v>46365</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3826,7 +3831,7 @@
       <c r="A35" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="13" t="n">
         <v>46366</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -3923,7 +3928,7 @@
       <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="13" t="n">
         <v>46367</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -4020,7 +4025,7 @@
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="12" t="n">
         <v>46370</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -4107,7 +4112,7 @@
       <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="13" t="n">
         <v>46371</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -4204,7 +4209,7 @@
       <c r="A39" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="13" t="n">
         <v>46372</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -4301,7 +4306,7 @@
       <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="13" t="n">
         <v>46373</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -4398,7 +4403,7 @@
       <c r="A41" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="13" t="n">
         <v>46374</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -4499,7 +4504,7 @@
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="n">
+      <c r="B42" s="12" t="n">
         <v>46377</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4586,7 +4591,7 @@
       <c r="A43" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="13" t="n">
         <v>46378</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -4683,7 +4688,7 @@
       <c r="A44" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="13" t="n">
         <v>46379</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -4780,7 +4785,7 @@
       <c r="A45" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="13" t="n">
         <v>46380</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -4877,7 +4882,7 @@
       <c r="A46" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="13" t="n">
         <v>46381</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -4978,7 +4983,7 @@
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="n">
+      <c r="B47" s="12" t="n">
         <v>46384</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -5067,7 +5072,7 @@
       <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="13" t="n">
         <v>46385</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -5168,7 +5173,7 @@
       <c r="A49" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="13" t="n">
         <v>46386</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -5265,7 +5270,7 @@
       <c r="A50" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="13" t="n">
         <v>46387</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -5362,7 +5367,7 @@
       <c r="A51" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="13" t="n">
         <v>46388</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -5459,7 +5464,7 @@
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B52" s="12" t="n">
         <v>46391</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -5549,7 +5554,7 @@
       <c r="A53" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="13" t="n">
         <v>46392</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -5646,7 +5651,7 @@
       <c r="A54" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="13" t="n">
         <v>46393</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -5743,7 +5748,7 @@
       <c r="A55" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="13" t="n">
         <v>46394</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -5840,7 +5845,7 @@
       <c r="A56" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="13" t="n">
         <v>46395</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -5937,7 +5942,7 @@
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="3" t="n">
+      <c r="B57" s="12" t="n">
         <v>46398</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -6025,7 +6030,7 @@
       <c r="A58" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="13" t="n">
         <v>46399</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -6122,7 +6127,7 @@
       <c r="A59" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="13" t="n">
         <v>46400</v>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -6219,7 +6224,7 @@
       <c r="A60" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="13" t="n">
         <v>46401</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -6316,7 +6321,7 @@
       <c r="A61" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="13" t="n">
         <v>46402</v>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -6413,7 +6418,7 @@
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="3" t="n">
+      <c r="B62" s="12" t="n">
         <v>46405</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -6500,7 +6505,7 @@
       <c r="A63" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="13" t="n">
         <v>46406</v>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -6597,7 +6602,7 @@
       <c r="A64" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="13" t="n">
         <v>46407</v>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -6700,7 +6705,7 @@
       <c r="A65" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="13" t="n">
         <v>46408</v>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -6797,7 +6802,7 @@
       <c r="A66" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="13" t="n">
         <v>46409</v>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -6894,7 +6899,7 @@
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B67" s="12" t="n">
         <v>46412</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -6981,7 +6986,7 @@
       <c r="A68" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="6" t="n">
+      <c r="B68" s="13" t="n">
         <v>46413</v>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -7078,7 +7083,7 @@
       <c r="A69" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="6" t="n">
+      <c r="B69" s="13" t="n">
         <v>46414</v>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -7175,7 +7180,7 @@
       <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="6" t="n">
+      <c r="B70" s="13" t="n">
         <v>46415</v>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -7276,7 +7281,7 @@
       <c r="A71" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="6" t="n">
+      <c r="B71" s="13" t="n">
         <v>46416</v>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -7377,7 +7382,7 @@
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="3" t="n">
+      <c r="B72" s="12" t="n">
         <v>46419</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -7463,7 +7468,7 @@
       <c r="A73" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="6" t="n">
+      <c r="B73" s="13" t="n">
         <v>46420</v>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -7564,7 +7569,7 @@
       <c r="A74" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="6" t="n">
+      <c r="B74" s="13" t="n">
         <v>46421</v>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -7665,7 +7670,7 @@
       <c r="A75" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="6" t="n">
+      <c r="B75" s="13" t="n">
         <v>46422</v>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -7766,7 +7771,7 @@
       <c r="A76" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="6" t="n">
+      <c r="B76" s="13" t="n">
         <v>46423</v>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -7863,7 +7868,7 @@
       <c r="A77" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="6" t="n">
+      <c r="B77" s="13" t="n">
         <v>46426</v>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -7960,7 +7965,7 @@
       <c r="A78" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="6" t="n">
+      <c r="B78" s="13" t="n">
         <v>46427</v>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -8057,7 +8062,7 @@
       <c r="A79" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="6" t="n">
+      <c r="B79" s="13" t="n">
         <v>46428</v>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -8154,7 +8159,7 @@
       <c r="A80" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="6" t="n">
+      <c r="B80" s="13" t="n">
         <v>46429</v>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -8259,7 +8264,7 @@
       <c r="A81" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="6" t="n">
+      <c r="B81" s="13" t="n">
         <v>46430</v>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -8364,7 +8369,7 @@
       <c r="A82" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="6" t="n">
+      <c r="B82" s="13" t="n">
         <v>46433</v>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -8461,7 +8466,7 @@
       <c r="A83" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="6" t="n">
+      <c r="B83" s="13" t="n">
         <v>46434</v>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -8564,7 +8569,7 @@
       <c r="A84" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="6" t="n">
+      <c r="B84" s="13" t="n">
         <v>46435</v>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -8665,7 +8670,7 @@
       <c r="A85" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="6" t="n">
+      <c r="B85" s="13" t="n">
         <v>46436</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -8762,7 +8767,7 @@
       <c r="A86" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="6" t="n">
+      <c r="B86" s="13" t="n">
         <v>46437</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -8859,7 +8864,7 @@
       <c r="A87" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="6" t="n">
+      <c r="B87" s="13" t="n">
         <v>46440</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -8956,7 +8961,7 @@
       <c r="A88" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="6" t="n">
+      <c r="B88" s="13" t="n">
         <v>46441</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -9059,7 +9064,7 @@
       <c r="A89" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="6" t="n">
+      <c r="B89" s="13" t="n">
         <v>46442</v>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -9160,7 +9165,7 @@
       <c r="A90" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="6" t="n">
+      <c r="B90" s="13" t="n">
         <v>46443</v>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -9261,7 +9266,7 @@
       <c r="A91" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="6" t="n">
+      <c r="B91" s="13" t="n">
         <v>46444</v>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -9362,7 +9367,7 @@
       <c r="A92" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="6" t="n">
+      <c r="B92" s="13" t="n">
         <v>46447</v>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -9459,7 +9464,7 @@
       <c r="A93" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="6" t="n">
+      <c r="B93" s="13" t="n">
         <v>46448</v>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -9556,7 +9561,7 @@
       <c r="A94" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="6" t="n">
+      <c r="B94" s="13" t="n">
         <v>46449</v>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -9653,7 +9658,7 @@
       <c r="A95" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="6" t="n">
+      <c r="B95" s="13" t="n">
         <v>46450</v>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -9750,7 +9755,7 @@
       <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="6" t="n">
+      <c r="B96" s="13" t="n">
         <v>46451</v>
       </c>
       <c r="C96" s="5" t="inlineStr">

--- a/data/content_plan.xlsx
+++ b/data/content_plan.xlsx
@@ -631,11 +631,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -722,11 +722,11 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="n">
-        <v>46322</v>
+        <v>46321</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -819,11 +819,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="13" t="n">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -916,11 +916,11 @@
         <v>4</v>
       </c>
       <c r="B5" s="13" t="n">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1013,11 +1013,11 @@
         <v>5</v>
       </c>
       <c r="B6" s="13" t="n">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1110,11 +1110,11 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="n">
-        <v>46328</v>
+        <v>46325</v>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1200,11 +1200,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="13" t="n">
-        <v>46329</v>
+        <v>46328</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1297,11 +1297,11 @@
         <v>8</v>
       </c>
       <c r="B9" s="13" t="n">
-        <v>46330</v>
+        <v>46329</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1394,11 +1394,11 @@
         <v>9</v>
       </c>
       <c r="B10" s="13" t="n">
-        <v>46331</v>
+        <v>46330</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1495,11 +1495,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="13" t="n">
-        <v>46332</v>
+        <v>46331</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1592,11 +1592,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="n">
-        <v>46335</v>
+        <v>46332</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1682,11 +1682,11 @@
         <v>12</v>
       </c>
       <c r="B13" s="13" t="n">
-        <v>46336</v>
+        <v>46335</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1779,11 +1779,11 @@
         <v>13</v>
       </c>
       <c r="B14" s="13" t="n">
-        <v>46337</v>
+        <v>46336</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1876,11 +1876,11 @@
         <v>14</v>
       </c>
       <c r="B15" s="13" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1979,11 +1979,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="13" t="n">
-        <v>46339</v>
+        <v>46338</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -2082,11 +2082,11 @@
         <v>16</v>
       </c>
       <c r="B17" s="12" t="n">
-        <v>46342</v>
+        <v>46339</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2172,11 +2172,11 @@
         <v>17</v>
       </c>
       <c r="B18" s="13" t="n">
-        <v>46343</v>
+        <v>46342</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2273,11 +2273,11 @@
         <v>18</v>
       </c>
       <c r="B19" s="13" t="n">
-        <v>46344</v>
+        <v>46343</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2376,11 +2376,11 @@
         <v>19</v>
       </c>
       <c r="B20" s="13" t="n">
-        <v>46345</v>
+        <v>46344</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2473,11 +2473,11 @@
         <v>20</v>
       </c>
       <c r="B21" s="13" t="n">
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2570,11 +2570,11 @@
         <v>21</v>
       </c>
       <c r="B22" s="12" t="n">
-        <v>46349</v>
+        <v>46346</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2658,11 +2658,11 @@
         <v>22</v>
       </c>
       <c r="B23" s="13" t="n">
-        <v>46350</v>
+        <v>46349</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2759,11 +2759,11 @@
         <v>23</v>
       </c>
       <c r="B24" s="13" t="n">
-        <v>46351</v>
+        <v>46350</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2856,11 +2856,11 @@
         <v>24</v>
       </c>
       <c r="B25" s="13" t="n">
-        <v>46352</v>
+        <v>46351</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2953,11 +2953,11 @@
         <v>25</v>
       </c>
       <c r="B26" s="13" t="n">
-        <v>46353</v>
+        <v>46352</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -3050,11 +3050,11 @@
         <v>26</v>
       </c>
       <c r="B27" s="12" t="n">
-        <v>46356</v>
+        <v>46353</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3140,11 +3140,11 @@
         <v>27</v>
       </c>
       <c r="B28" s="13" t="n">
-        <v>46357</v>
+        <v>46356</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -3237,11 +3237,11 @@
         <v>28</v>
       </c>
       <c r="B29" s="13" t="n">
-        <v>46358</v>
+        <v>46357</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -3344,11 +3344,11 @@
         <v>29</v>
       </c>
       <c r="B30" s="13" t="n">
-        <v>46359</v>
+        <v>46358</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -3441,11 +3441,11 @@
         <v>30</v>
       </c>
       <c r="B31" s="13" t="n">
-        <v>46360</v>
+        <v>46359</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -3542,11 +3542,11 @@
         <v>31</v>
       </c>
       <c r="B32" s="12" t="n">
-        <v>46363</v>
+        <v>46360</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3632,11 +3632,11 @@
         <v>32</v>
       </c>
       <c r="B33" s="13" t="n">
-        <v>46364</v>
+        <v>46363</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -3729,11 +3729,11 @@
         <v>33</v>
       </c>
       <c r="B34" s="13" t="n">
-        <v>46365</v>
+        <v>46364</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -3832,11 +3832,11 @@
         <v>34</v>
       </c>
       <c r="B35" s="13" t="n">
-        <v>46366</v>
+        <v>46365</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -3929,11 +3929,11 @@
         <v>35</v>
       </c>
       <c r="B36" s="13" t="n">
-        <v>46367</v>
+        <v>46366</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -4026,11 +4026,11 @@
         <v>36</v>
       </c>
       <c r="B37" s="12" t="n">
-        <v>46370</v>
+        <v>46367</v>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4113,11 +4113,11 @@
         <v>37</v>
       </c>
       <c r="B38" s="13" t="n">
-        <v>46371</v>
+        <v>46370</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -4210,11 +4210,11 @@
         <v>38</v>
       </c>
       <c r="B39" s="13" t="n">
-        <v>46372</v>
+        <v>46371</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -4307,11 +4307,11 @@
         <v>39</v>
       </c>
       <c r="B40" s="13" t="n">
-        <v>46373</v>
+        <v>46372</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -4404,11 +4404,11 @@
         <v>40</v>
       </c>
       <c r="B41" s="13" t="n">
-        <v>46374</v>
+        <v>46373</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -4505,11 +4505,11 @@
         <v>41</v>
       </c>
       <c r="B42" s="12" t="n">
-        <v>46377</v>
+        <v>46374</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4592,11 +4592,11 @@
         <v>42</v>
       </c>
       <c r="B43" s="13" t="n">
-        <v>46378</v>
+        <v>46377</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -4689,11 +4689,11 @@
         <v>43</v>
       </c>
       <c r="B44" s="13" t="n">
-        <v>46379</v>
+        <v>46378</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -4786,11 +4786,11 @@
         <v>44</v>
       </c>
       <c r="B45" s="13" t="n">
-        <v>46380</v>
+        <v>46379</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -4883,11 +4883,11 @@
         <v>45</v>
       </c>
       <c r="B46" s="13" t="n">
-        <v>46381</v>
+        <v>46380</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -4984,11 +4984,11 @@
         <v>46</v>
       </c>
       <c r="B47" s="12" t="n">
-        <v>46384</v>
+        <v>46381</v>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5073,11 +5073,11 @@
         <v>47</v>
       </c>
       <c r="B48" s="13" t="n">
-        <v>46385</v>
+        <v>46384</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -5174,11 +5174,11 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="n">
-        <v>46386</v>
+        <v>46385</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -5271,11 +5271,11 @@
         <v>49</v>
       </c>
       <c r="B50" s="13" t="n">
-        <v>46387</v>
+        <v>46386</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -5368,11 +5368,11 @@
         <v>50</v>
       </c>
       <c r="B51" s="13" t="n">
-        <v>46388</v>
+        <v>46387</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -5465,11 +5465,11 @@
         <v>51</v>
       </c>
       <c r="B52" s="12" t="n">
-        <v>46391</v>
+        <v>46388</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -5555,11 +5555,11 @@
         <v>52</v>
       </c>
       <c r="B53" s="13" t="n">
-        <v>46392</v>
+        <v>46391</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -5652,11 +5652,11 @@
         <v>53</v>
       </c>
       <c r="B54" s="13" t="n">
-        <v>46393</v>
+        <v>46392</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -5749,11 +5749,11 @@
         <v>54</v>
       </c>
       <c r="B55" s="13" t="n">
-        <v>46394</v>
+        <v>46393</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -5846,11 +5846,11 @@
         <v>55</v>
       </c>
       <c r="B56" s="13" t="n">
-        <v>46395</v>
+        <v>46394</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -5943,11 +5943,11 @@
         <v>56</v>
       </c>
       <c r="B57" s="12" t="n">
-        <v>46398</v>
+        <v>46395</v>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -6031,11 +6031,11 @@
         <v>57</v>
       </c>
       <c r="B58" s="13" t="n">
-        <v>46399</v>
+        <v>46398</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -6128,11 +6128,11 @@
         <v>58</v>
       </c>
       <c r="B59" s="13" t="n">
-        <v>46400</v>
+        <v>46399</v>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -6225,11 +6225,11 @@
         <v>59</v>
       </c>
       <c r="B60" s="13" t="n">
-        <v>46401</v>
+        <v>46400</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -6322,11 +6322,11 @@
         <v>60</v>
       </c>
       <c r="B61" s="13" t="n">
-        <v>46402</v>
+        <v>46401</v>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -6419,11 +6419,11 @@
         <v>61</v>
       </c>
       <c r="B62" s="12" t="n">
-        <v>46405</v>
+        <v>46402</v>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -6506,11 +6506,11 @@
         <v>62</v>
       </c>
       <c r="B63" s="13" t="n">
-        <v>46406</v>
+        <v>46405</v>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -6603,11 +6603,11 @@
         <v>63</v>
       </c>
       <c r="B64" s="13" t="n">
-        <v>46407</v>
+        <v>46406</v>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -6706,11 +6706,11 @@
         <v>64</v>
       </c>
       <c r="B65" s="13" t="n">
-        <v>46408</v>
+        <v>46407</v>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -6803,11 +6803,11 @@
         <v>65</v>
       </c>
       <c r="B66" s="13" t="n">
-        <v>46409</v>
+        <v>46408</v>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -6900,11 +6900,11 @@
         <v>66</v>
       </c>
       <c r="B67" s="12" t="n">
-        <v>46412</v>
+        <v>46409</v>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -6987,11 +6987,11 @@
         <v>67</v>
       </c>
       <c r="B68" s="13" t="n">
-        <v>46413</v>
+        <v>46412</v>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -7084,11 +7084,11 @@
         <v>68</v>
       </c>
       <c r="B69" s="13" t="n">
-        <v>46414</v>
+        <v>46413</v>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -7181,11 +7181,11 @@
         <v>69</v>
       </c>
       <c r="B70" s="13" t="n">
-        <v>46415</v>
+        <v>46414</v>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -7282,11 +7282,11 @@
         <v>70</v>
       </c>
       <c r="B71" s="13" t="n">
-        <v>46416</v>
+        <v>46415</v>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -7383,11 +7383,11 @@
         <v>71</v>
       </c>
       <c r="B72" s="12" t="n">
-        <v>46419</v>
+        <v>46416</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -7469,11 +7469,11 @@
         <v>72</v>
       </c>
       <c r="B73" s="13" t="n">
-        <v>46420</v>
+        <v>46419</v>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -7570,11 +7570,11 @@
         <v>73</v>
       </c>
       <c r="B74" s="13" t="n">
-        <v>46421</v>
+        <v>46420</v>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -7671,11 +7671,11 @@
         <v>74</v>
       </c>
       <c r="B75" s="13" t="n">
-        <v>46422</v>
+        <v>46421</v>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -7772,11 +7772,11 @@
         <v>75</v>
       </c>
       <c r="B76" s="13" t="n">
-        <v>46423</v>
+        <v>46422</v>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -7869,11 +7869,11 @@
         <v>76</v>
       </c>
       <c r="B77" s="13" t="n">
-        <v>46426</v>
+        <v>46423</v>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -7966,11 +7966,11 @@
         <v>77</v>
       </c>
       <c r="B78" s="13" t="n">
-        <v>46427</v>
+        <v>46426</v>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -8063,11 +8063,11 @@
         <v>78</v>
       </c>
       <c r="B79" s="13" t="n">
-        <v>46428</v>
+        <v>46427</v>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -8160,11 +8160,11 @@
         <v>79</v>
       </c>
       <c r="B80" s="13" t="n">
-        <v>46429</v>
+        <v>46428</v>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -8265,11 +8265,11 @@
         <v>80</v>
       </c>
       <c r="B81" s="13" t="n">
-        <v>46430</v>
+        <v>46429</v>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -8370,11 +8370,11 @@
         <v>81</v>
       </c>
       <c r="B82" s="13" t="n">
-        <v>46433</v>
+        <v>46430</v>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -8467,11 +8467,11 @@
         <v>82</v>
       </c>
       <c r="B83" s="13" t="n">
-        <v>46434</v>
+        <v>46433</v>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -8570,11 +8570,11 @@
         <v>83</v>
       </c>
       <c r="B84" s="13" t="n">
-        <v>46435</v>
+        <v>46434</v>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -8671,11 +8671,11 @@
         <v>84</v>
       </c>
       <c r="B85" s="13" t="n">
-        <v>46436</v>
+        <v>46435</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -8768,11 +8768,11 @@
         <v>85</v>
       </c>
       <c r="B86" s="13" t="n">
-        <v>46437</v>
+        <v>46436</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -8865,11 +8865,11 @@
         <v>86</v>
       </c>
       <c r="B87" s="13" t="n">
-        <v>46440</v>
+        <v>46437</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -8962,11 +8962,11 @@
         <v>87</v>
       </c>
       <c r="B88" s="13" t="n">
-        <v>46441</v>
+        <v>46440</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -9065,11 +9065,11 @@
         <v>88</v>
       </c>
       <c r="B89" s="13" t="n">
-        <v>46442</v>
+        <v>46441</v>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -9166,11 +9166,11 @@
         <v>89</v>
       </c>
       <c r="B90" s="13" t="n">
-        <v>46443</v>
+        <v>46442</v>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -9267,11 +9267,11 @@
         <v>90</v>
       </c>
       <c r="B91" s="13" t="n">
-        <v>46444</v>
+        <v>46443</v>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -9368,11 +9368,11 @@
         <v>91</v>
       </c>
       <c r="B92" s="13" t="n">
-        <v>46447</v>
+        <v>46444</v>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -9465,11 +9465,11 @@
         <v>92</v>
       </c>
       <c r="B93" s="13" t="n">
-        <v>46448</v>
+        <v>46447</v>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -9562,11 +9562,11 @@
         <v>93</v>
       </c>
       <c r="B94" s="13" t="n">
-        <v>46449</v>
+        <v>46448</v>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -9659,11 +9659,11 @@
         <v>94</v>
       </c>
       <c r="B95" s="13" t="n">
-        <v>46450</v>
+        <v>46449</v>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -9756,11 +9756,11 @@
         <v>95</v>
       </c>
       <c r="B96" s="13" t="n">
-        <v>46451</v>
+        <v>46450</v>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">

--- a/data/content_plan.xlsx
+++ b/data/content_plan.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dsg #дсг #роботдсг #мехатроник #dq250 #golf #skoda #запчастидляакпп #автозапчасти #0b5</t>
+          <t>#leoparts #dsg #дсг #роботдсг #мехатроник</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
@@ -789,7 +789,7 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #skoda #volkswagen #запчастидляавто #запчастиванкпп #0am325025h</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #dq200dsg7 #роботдсг #мехатроник #ремонтмехатроника #запчастимехатроника #электроннаяплата #audi #vag #ремонтавто #запчастидляавто #0am325025hx</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #dq200dsg7</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #seat #golf #автозапчастивналичии #ремонтавто #0am325025x</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #0am #dq200dsg7 #мехатроник #ремонтмехатроника #запчастимехатроника #электроннаяплата #golf #skoda #автозапчастивналичии #запчастидляавто #0am927769d</t>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #0am</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #dq200dsg7 #ремонтdq200 #мехатроник #устройствомехатроника #советыавтовладельцам #ремонтмехатроника #skoda #seat #автомастер #запчастиванкпп</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #dq200dsg7</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq250 #dsg6 #дсг6 #ремонтdq250 #02e #мехатроник #ремонтмехатроника #запчастимехатроника #tiguan #volkswagen #запчастидляакпп #автомастер #02e927770al</t>
+          <t>#leoparts #dq250 #dsg6 #дсг6 #ремонтdq250</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw #роботдсг #мехатроник #ремонтмехатроника #запчастимехатроника #ремкомплект #octavia #skoda #запчастидляавто #автозапчастивналичии #0am325025</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw</t>
         </is>
       </c>
       <c r="O9" s="5" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0am #ремонтdq200 #ремкомплект #ремкомплектмехатроника #volkswagen #polo #запчастиванкпп #автозапчастивналичии #0cw0am325025</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0am</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw #dq200dsg7 #уплотнение #прокладка #ремкомплект #ремкомплектмехатроника #octavia #polo #ремонтавто #автосервис #0am325025m</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw</t>
         </is>
       </c>
       <c r="O11" s="5" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dq250 #dsg6 #dq250dsg6 #дсг6 #мехатроникdq250 #dq200 #dq500 #какоткрытьdsg #passat #seat #запчастиванкпп #автозапчастивналичии</t>
+          <t>#leoparts #dq250 #dsg6 #dq250dsg6 #дсг6</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #дсг7 #роботдсг #гидроплита #усиленнаягидроплита #ремонтмехатроника #polo #audi #автосервис #автомастер #0am325066ae</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #дсг7</t>
         </is>
       </c>
       <c r="O13" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0am #0cw #гидроплита #усиленнаягидроплита #vag #seat #ремонтавто #автосервис</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0am</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw #dq200dsg7 #гидроплита #усиленнаягидроплита #ремонтмехатроника #фильтрdsg #seat #polo #запчастиванкпп #автозапчасти</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw</t>
         </is>
       </c>
       <c r="O15" s="5" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #ремонтdq200 #дсг7 #сальник #течьмасла #сальникштока #пыльник #volkswagen #golf #ремонтавто #автосервис</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #ремонтdq200</t>
         </is>
       </c>
       <c r="O16" s="5" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dq250 #dsg6 #dq250dsg6 #ремонтdq250 #мехатроникdq250 #skoda #golf #автозапчастивналичии #запчастидляавто</t>
+          <t>#leoparts #dq250 #dsg6 #dq250dsg6 #ремонтdq250</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #роботдсг #дсг7 #golf #volkswagen #ремонтавто #запчастиванкпп</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #роботдсг</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #мехатроникdq200 #ремонтdq200 #сальник #течьмасла #сальникштока #пыльник #octavia #vag #автозапчастивналичии #автозапчасти</t>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #мехатроникdq200</t>
         </is>
       </c>
       <c r="O19" s="5" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #дсг7 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #skoda #audi #автомастер #ремонтакпп #0am325091e</t>
+          <t>#leoparts #dq200 #dsg7 #0am #дсг7</t>
         </is>
       </c>
       <c r="O20" s="5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг #0cw #шток #штокмехатроника #усиленныйшток #polo #octavia #запчастиванкпп #ремонтакпп #0am325091f</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг</t>
         </is>
       </c>
       <c r="O21" s="5" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw #роботдсг #мехатроник #ремонтмехатроника #запчастимехатроника #volkswagen #skoda #автомастер #автозапчасти</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #0am #мехатроникdq200 #шток #штокмехатроника #усиленныйшток #втулкиштоков #golf #audi #запчастидляакпп #ремонтавто #0am325091eset</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #0am</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #роботдсг #0am #шток #штокмехатроника #усиленныйшток #втулкиштоков #polo #seat #автозапчастивналичии #запчастидляакпп #0am325025u</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #роботдсг</t>
         </is>
       </c>
       <c r="O24" s="5" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #мехатроникdq200 #дсг7 #шток #штокмехатроника #усиленныйшток #втулкиштоков #skoda #audi #запчастидляакпп #автомастер #0am325025z</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #мехатроникdq200</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг #0am #шток #штокмехатроника #усиленныйшток #втулкиштоков #audi #octavia #запчастиванкпп #ремонтакпп #0am325025d</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг</t>
         </is>
       </c>
       <c r="O26" s="5" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dsg #дсг #роботдсг #dq500 #dq200 #skoda #passat #запчастидляакпп #запчастидляавто</t>
+          <t>#leoparts #dsg #дсг #роботдсг #dq500</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #0cw #роботдсг #шток #штокмехатроника #усиленныйшток #втулкиштоков #audi #seat #автозапчастивналичии #запчастидляавто</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #0cw</t>
         </is>
       </c>
       <c r="O28" s="5" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #ремонтdq200 #мехатроникdq200 #втулкиштоков #гильзаштока #прокладка #прокладкамехатроника #skoda #audi #ремонтавто #запчастидляакпп</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #ремонтdq200</t>
         </is>
       </c>
       <c r="O29" s="5" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #мехатроникdq200 #дсг7 #шток #штокмехатроника #усиленныйшток #volkswagen #golf #запчастидляавто #ремонтакпп #0am325066ac</t>
+          <t>#leoparts #dq200 #dsg7 #0am #мехатроникdq200</t>
         </is>
       </c>
       <c r="O30" s="5" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #роботдсг #ремонтdq200 #шток #штокмехатроника #усиленныйшток #ремкомплект #polo #audi #автозапчасти #автосервис</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #роботдсг</t>
         </is>
       </c>
       <c r="O31" s="5" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dsg #дсг #мехатроник #dq250 #dq500 #ремонтмехатроника #запчастимехатроника #ремкомплект #volkswagen #passat #автосервис #автозапчасти</t>
+          <t>#leoparts #dsg #дсг #мехатроник #dq250</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="N33" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #мехатроникdq200 #роботдсг #толкатель #толкателивилок #сальникитолкателя #skoda #octavia #запчастидляакпп #ремонтавто #0am325025l</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #мехатроникdq200</t>
         </is>
       </c>
       <c r="O33" s="5" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #мехатроникdq200 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #сальник #skoda #volkswagen #запчастидляавто #запчастиванкпп</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #мехатроникdq200</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #роботдсг #ремонтdq200 #шток #штокмехатроника #усиленныйшток #сальник #seat #octavia #автомастер #автозапчасти</t>
+          <t>#leoparts #dq200 #dsg7 #0am #роботдсг</t>
         </is>
       </c>
       <c r="O35" s="5" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #0am #дсг7 #шток #штокмехатроника #усиленныйшток #сальник #audi #golf #запчастидляакпп #ремонтакпп</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #0am</t>
         </is>
       </c>
       <c r="O36" s="5" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dq250 #dsg6 #дсг6 #dq250dsg6 #ремонтdq250 #фильтрdsg #масляныйфильтр #корпусфильтра #golf #tiguan #ремонтакпп #автозапчастивналичии</t>
+          <t>#leoparts #dq250 #dsg6 #дсг6 #dq250dsg6</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="N38" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #dq200dsg7 #роботдсг #шток #штокмехатроника #усиленныйшток #сальник #volkswagen #polo #запчастидляакпп #автосервис #0am325066ad</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #dq200dsg7</t>
         </is>
       </c>
       <c r="O38" s="5" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #мехатроникdq200 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #пыльник #golf #polo #запчастиванкпп #автозапчастивналичии #122390akaf</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #мехатроникdq200</t>
         </is>
       </c>
       <c r="O39" s="5" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw #0am #шток #штокмехатроника #усиленныйшток #пыльник #polo #volkswagen #запчастиванкпп #автосервис #122390akaf</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #дсг7 #ремонтdq200 #пыльник #пыльникштока #polo #volkswagen #ремонтакпп #ремонтавто</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #дсг7</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dsg #дсг #роботдсг #ремонтdsg #dq500 #шток #штокмехатроника #усиленныйшток #втулкиштоков #seat #vag #автозапчастивналичии #автомастер</t>
+          <t>#leoparts #dsg #дсг #роботдсг #ремонтdsg</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr"/>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #0cw #ремонтdq200 #шток #штокмехатроника #усиленныйшток #крышкамехатроника #volkswagen #skoda #запчастидляакпп #запчастидляавто #0am325025q</t>
+          <t>#leoparts #dq200 #dsg7 #0am #0cw</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #dq200dsg7 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #ремкомплект #seat #vag #автозапчастивналичии #запчастидляавто #0am325025g</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #dq200dsg7</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200 #0cw #шток #штокмехатроника #усиленныйшток #ремкомплект #octavia #volkswagen #ремонтакпп #ремонтавто #0am325025hfe</t>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200</t>
         </is>
       </c>
       <c r="O45" s="5" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #дсг7 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #ремкомплект #polo #skoda #запчастиванкпп #ремонтакпп</t>
+          <t>#leoparts #dq200 #dsg7 #0am #дсг7</t>
         </is>
       </c>
       <c r="O46" s="5" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #dq200dsg7 #дсг7 #мехатроник #ремонтмехатроника #запчастимехатроника #audi #polo #автозапчастивналичии #запчастидляавто</t>
+          <t>#leoparts #dq200 #dsg7 #0am #dq200dsg7</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr"/>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200 #0cw #шток #штокмехатроника #усиленныйшток #клипсы #seat #octavia #автозапчастивналичии #запчастиванкпп #0am325025p</t>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #ремонтdq200 #dq200dsg7 #сальник #течьмасла #сальникштока #толкатель #polo #skoda #ремонтакпп #автозапчасти #0am325413a</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #ремонтdq200</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #дсг7 #роботдсг #сальник #течьмасла #сальникштока #толкатель #seat #skoda #ремонтавто #запчастиванкпп</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #дсг7</t>
         </is>
       </c>
       <c r="O50" s="5" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #dq200dsg7 #0cw #сальник #течьмасла #сальникштока #seat #vag #запчастиванкпп #запчастидляавто</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #dq200dsg7</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dsg #дсг #роботдсг #dq200 #dq250 #электроннаяплата #блокуправленияdsg #passat #vag #запчастидляавто #автозапчасти</t>
+          <t>#leoparts #dsg #дсг #роботдсг #dq200</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr"/>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #дсг7 #ремонтdq200 #сальник #течьмасла #сальникштока #толкатель #golf #seat #автомастер #автосервис</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #дсг7</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #мехатроникdq200 #0cw #golf #volkswagen #автозапчасти #ремонтакпп</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #мехатроникdq200</t>
         </is>
       </c>
       <c r="O54" s="5" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #мехатроникdq200 #ремонтdq200 #толкатель #толкателивилок #сальникитолкателя #уплотнительноекольцо #volkswagen #octavia #ремонтакпп #запчастидляакпп #0am325025r</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #мехатроникdq200</t>
         </is>
       </c>
       <c r="O55" s="5" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #дсг7 #0cw #подшипник #подшипникивилки #golf #volkswagen #запчастидляавто #запчастидляакпп</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #дсг7</t>
         </is>
       </c>
       <c r="O56" s="5" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dsg #дсг #dq200 #ремонтdsg #роботдсг #volkswagen #skoda #ремонтакпп #ремонтавто</t>
+          <t>#leoparts #dsg #дсг #dq200 #ремонтdsg</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr"/>
@@ -6098,7 +6098,7 @@
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #ремонтdq200 #0cw #мехатроник #ремонтмехатроника #запчастимехатроника #крышкамехатроника #audi #octavia #запчастидляакпп #запчастиванкпп #0am325219c</t>
+          <t>#leoparts #dq200 #dsg7 #0am #ремонтdq200</t>
         </is>
       </c>
       <c r="O58" s="5" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #dq200dsg7 #0am #прокладка #прокладкамехатроника #крышкамехатроника #крышкаштока #audi #vag #автомастер #автозапчастивналичии #0am325443d</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #dq200dsg7</t>
         </is>
       </c>
       <c r="O59" s="5" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0am #0cw #прокладка #прокладкамехатроника #крышкамехатроника #крышкаштока #vag #volkswagen #автомастер #автосервис #0am325025ae</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0am</t>
         </is>
       </c>
       <c r="O60" s="5" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #0am #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #крышкамехатроника #polo #vag #автозапчасти #запчастидляавто</t>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #0am</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #dq250 #dsg6 #ремонтdq250 #02e #дсг6 #мехатроник #ремонтмехатроника #запчастимехатроника #vag #volkswagen #запчастидляакпп #запчастидляавто</t>
+          <t>#leoparts #dq250 #dsg6 #ремонтdq250 #02e</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #роботдсг #0am #мехатроник #ремонтмехатроника #запчастимехатроника #прокладка #octavia #vag #ремонтакпп #запчастиванкпп</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #роботдсг</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200 #0am #мехатроник #ремонтмехатроника #запчастимехатроника #крышкамехатроника #audi #volkswagen #запчастиванкпп #автомастер #01x301127c</t>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200</t>
         </is>
       </c>
       <c r="O64" s="5" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #dq200dsg7 #мехатроникdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #фильтрdsg #vag #audi #автосервис #запчастиванкпп #0am325433e</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #dq200dsg7</t>
         </is>
       </c>
       <c r="O65" s="5" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="N66" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #мехатроникdq200 #дсг7 #мехатроник #ремонтмехатроника #запчастимехатроника #фильтрdsg #volkswagen #audi #запчастидляавто #ремонтакпп</t>
+          <t>#leoparts #dq200 #dsg7 #0am #мехатроникdq200</t>
         </is>
       </c>
       <c r="O66" s="5" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #ea888 #ea888gen3 #корпусфильтра #18tsi #масляныйфильтр #passat #audi #автозапчасти #автозапчастивналичии</t>
+          <t>#leoparts #ea888 #ea888gen3 #корпусфильтра #18tsi</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr"/>
@@ -7054,7 +7054,7 @@
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq250 #dsg6 #мехатроникdq250 #ремонтdq250 #dq250dsg6 #фильтрdsg #масляныйфильтр #корпусфильтра #volkswagen #passat #запчастидляакпп #автосервис #02e305051c</t>
+          <t>#leoparts #dq250 #dsg6 #мехатроникdq250 #ремонтdq250</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="N69" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq500 #dsg7 #мокроесцепление #0bh #дсг7 #фильтрdsg #масляныйфильтр #корпусфильтра #tiguan #vag #автосервис #ремонтавто</t>
+          <t>#leoparts #dq500 #dsg7 #мокроесцепление #0bh</t>
         </is>
       </c>
       <c r="O69" s="5" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq250 #dsg6 #дсг6 #ремонтdq250 #мехатроникdq250 #фильтрdsg #масляныйфильтр #корпусфильтра #skoda #audi #автосервис #ремонтакпп #02e305045</t>
+          <t>#leoparts #dq250 #dsg6 #дсг6 #ремонтdq250</t>
         </is>
       </c>
       <c r="O70" s="5" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq500 #dsg7 #dq500dsg7 #ремонтdq500 #дсг7 #фильтрdsg #масляныйфильтр #корпусфильтра #skoda #volkswagen #автомастер #ремонтакпп #0bh325183</t>
+          <t>#leoparts #dq500 #dsg7 #dq500dsg7 #ремонтdq500</t>
         </is>
       </c>
       <c r="O71" s="5" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>#leoparts #вариатор #cvt #гидроблок #ремонтвариатора #jf015e #mitsubishi #duster #ремонтавто #автозапчасти</t>
+          <t>#leoparts #вариатор #cvt #гидроблок #ремонтвариатора</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr"/>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq500 #dsg7 #дсг7 #0bh #мокроесцепление #фильтрdsg #масляныйфильтр #корпусфильтра #volkswagen #passat #автомастер #автозапчастивналичии</t>
+          <t>#leoparts #dq500 #dsg7 #дсг7 #0bh</t>
         </is>
       </c>
       <c r="O73" s="5" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq500 #dsg7 #мокроесцепление #0bh #dq500dsg7 #фильтрdsg #масляныйфильтр #корпусфильтра #vag #volkswagen #автозапчасти #запчастидляакпп #0bh325159</t>
+          <t>#leoparts #dq500 #dsg7 #мокроесцепление #0bh</t>
         </is>
       </c>
       <c r="O74" s="5" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq500 #dsg7 #ремонтdq500 #dq500dsg7 #0bh #соленоиды #соленоидыdsg #фильтрdsg #масляныйфильтр #tiguan #volkswagen #запчастидляакпп #запчастидляавто #123014af</t>
+          <t>#leoparts #dq500 #dsg7 #ремонтdq500 #dq500dsg7</t>
         </is>
       </c>
       <c r="O75" s="5" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="N76" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200 #dq200dsg7 #соленоиды #соленоидыdsg #golf #audi #автосервис #автозапчасти #0am325025b</t>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200</t>
         </is>
       </c>
       <c r="O76" s="5" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="N77" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #роботдсг #dq200dsg7 #соленоиды #соленоидыdsg #polo #skoda #ремонтавто #запчастидляакпп #0am325025n</t>
+          <t>#leoparts #dq200 #dsg7 #0am #роботдсг</t>
         </is>
       </c>
       <c r="O77" s="5" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #dq200dsg7 #роботдсг #сепараторнаяпластина #пластинысоленоидов #skoda #vag #автозапчастивналичии #автосервис #0am325467j</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #dq200dsg7</t>
         </is>
       </c>
       <c r="O78" s="5" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #мехатроникdq200 #dq200dsg7 #сепараторнаяпластина #пластинысоленоидов #seat #volkswagen #запчастиванкпп #автосервис</t>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #мехатроникdq200</t>
         </is>
       </c>
       <c r="O79" s="5" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #роботдсг #0cw #соленоиды #соленоидыdsg #сепараторнаяпластина #пластинысоленоидов #golf #polo #запчастидляавто #автозапчасти #0am325025j</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #роботдсг</t>
         </is>
       </c>
       <c r="O80" s="5" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw #ремонтdq200 #соленоиды #соленоидыdsg #сепараторнаяпластина #пластинысоленоидов #seat #polo #ремонтакпп #ремонтавто</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw</t>
         </is>
       </c>
       <c r="O81" s="5" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="N82" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0am #мехатроникdq200 #роботдсг #соленоиды #соленоидыdsg #сепараторнаяпластина #пластинысоленоидов #seat #volkswagen #автомастер #запчастиванкпп</t>
+          <t>#leoparts #dq200 #dsg7 #0am #мехатроникdq200</t>
         </is>
       </c>
       <c r="O82" s="5" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #0am #0cw #соленоиды #соленоидыdsg #планкасоленоидов #skoda #volkswagen #автосервис #автозапчасти #0am325477ae</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #0am</t>
         </is>
       </c>
       <c r="O83" s="5" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="N84" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #дсг7 #мехатроникdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #гидроаккумулятор #skoda #polo #автосервис #запчастидляавто #0am325587e</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #дсг7</t>
         </is>
       </c>
       <c r="O84" s="5" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="N85" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #дсг7 #роботдсг #гидроаккумулятор #уплотнительноекольцо #golf #polo #запчастидляакпп #автозапчасти #0am325025с</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #дсг7</t>
         </is>
       </c>
       <c r="O85" s="5" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="N86" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw #мехатроникdq200 #прокладка #прокладкамехатроника #электроннаяплата #блокуправленияdsg #volkswagen #polo #ремонтакпп #автозапчасти #0am927769n</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw</t>
         </is>
       </c>
       <c r="O86" s="5" t="inlineStr">
@@ -8932,7 +8932,7 @@
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #мехатроникdq200 #роботдсг #прокладка #прокладкамехатроника #электроннаяплата #блокуправленияdsg #seat #octavia #запчастидляакпп #запчастидляавто #0cw325025h</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #мехатроникdq200</t>
         </is>
       </c>
       <c r="O87" s="5" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #0am #ремонтdq200 #уплотнение #прокладка #skoda #volkswagen #автозапчасти #запчастидляакпп #0cw0amdsgdq200</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #0am</t>
         </is>
       </c>
       <c r="O88" s="5" t="inlineStr">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #ремонтdq200 #дсг7 #мехатроник #ремонтмехатроника #запчастимехатроника #заглушкакпп #skoda #seat #ремонтакпп #автомастер #0am301212a</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #ремонтdq200</t>
         </is>
       </c>
       <c r="O89" s="5" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="N90" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0am #ремонтdq200 #сальник #течьмасла #сальникштока #сальникпривода #octavia #volkswagen #запчастиванкпп #автомастер</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0am</t>
         </is>
       </c>
       <c r="O90" s="5" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="N91" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #0am #мехатроникdq200 #сальник #течьмасла #сальникштока #audi #vag #ремонтавто #автомастер</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #0am</t>
         </is>
       </c>
       <c r="O91" s="5" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #вариатор #cvt #re0f11a #гидроблок #jf015e #qashqai #mitsubishi #автозапчастивналичии #ремонтавто #317053tx0c</t>
+          <t>#leoparts #вариатор #cvt #re0f11a #гидроблок</t>
         </is>
       </c>
       <c r="O92" s="5" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="N93" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #ea888 #ea888gen3 #18tsi #двигательea888 #масляныйфильтр #корпусфильтра #volkswagen #octavia #запчастидляакпп #запчастиванкпп</t>
+          <t>#leoparts #ea888 #ea888gen3 #18tsi #двигательea888</t>
         </is>
       </c>
       <c r="O93" s="5" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #ea888 #ea888gen3 #20tsi #tsi #18tsi #масляныйфильтр #корпусфильтра #обратныйклапан #octavia #passat #ремонтакпп #автозапчастивналичии</t>
+          <t>#leoparts #ea888 #ea888gen3 #20tsi #tsi</t>
         </is>
       </c>
       <c r="O94" s="5" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="N95" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #ea888 #ea888gen3 #tsi #двигательea888 #масляныйфильтр #обратныйклапан #tiguan #skoda #запчастидляавто #автозапчасти</t>
+          <t>#leoparts #ea888 #ea888gen3 #tsi #двигательea888</t>
         </is>
       </c>
       <c r="O95" s="5" t="inlineStr">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #gm #распредвал #датчикраспредвала #импульсноекольцо #chevrolet #уплотнительноекольцо #opel #запчастиванкпп #запчастидляакпп #55565480</t>
+          <t>#leoparts #gm #распредвал #датчикраспредвала #импульсноекольцо</t>
         </is>
       </c>
       <c r="O96" s="5" t="inlineStr">

--- a/data/content_plan.xlsx
+++ b/data/content_plan.xlsx
@@ -636,11 +636,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -727,11 +727,11 @@
         <v>33</v>
       </c>
       <c r="B3" s="13" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -827,64 +827,574 @@
     </row>
     <row r="4" ht="175.5" customHeight="1">
       <c r="A4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>46321</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Пн</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Instagram + VK</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроники</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>0am325025H</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроник DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Проверен на стенде и на авто</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>• Тест на специальном стенде для DQ200
+• После сборки обкатка на дороге, не на подъёмнике
+• Для коробок 0AM / 0CW</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>photos/0am325025H/ — 6 шт.</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>Готовый мехатроник для DQ200 — каждый после сборки проверяем на стенде и обкатываем на автомобиле 🚗
+🔹 Тест на специальном стенде для DQ200
+🔹 После сборки обкатка на дороге, не на подъёмнике
+🔹 Для коробок 0AM / 0CW
+✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
+🔩 Артикул: 0am325025H
+📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #skoda #volkswagen #запчастидляавто #запчастиванкпп #0am325025h</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>68 800</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="n"/>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>не опубликовано</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="175.5" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>46322</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Вт</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Instagram + VK</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроники</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>0AM927769D</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>DSG7 DQ200 · 0AM927769D</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>• Блок управления мехатроника DSG7
+• Для Volkswagen, Audi, Skoda, Seat
+• Артикул 0AM927769D</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>photos/0AM927769D/ — 1 шт.</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200 — блок управления вашей коробкой 🧠
+🔹 Блок управления мехатроника DSG7
+🔹 Для Volkswagen, Audi, Skoda, Seat
+🔹 Артикул 0AM927769D
+✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
+🔩 Артикул: 0AM927769D
+📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #0am #dq200dsg7 #мехатроник #ремонтмехатроника #запчастимехатроника #электроннаяплата #golf #skoda #автозапчастивналичии #запчастидляавто #0am927769d</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>78 800</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Q5" s="7" t="n"/>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>не опубликовано</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="175.5" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>46323</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Ср</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Instagram + VK</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроники</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>0am325025HX</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 в сборе с платой</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Электронная плата 0AM927769D</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>• Каждый соленоид проверен на стенде
+• Каждый мехатроник проверяется на авто после сборки
+• Плата уже установлена</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>photos/0am325025HX/ — 4 шт.</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроник в сборе с электронной платой — ставите и едете. Проверка на стенде и на авто 🔧
+🔹 Каждый соленоид проверен на стенде
+🔹 Каждый мехатроник проверяется на авто после сборки
+🔹 Плата уже установлена
+✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
+🔩 Артикул: 0am325025HX
+📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>#leoparts #dq200 #dsg7 #0cw #dq200dsg7 #роботдсг #мехатроник #ремонтмехатроника #запчастимехатроника #электроннаяплата #audi #vag #ремонтавто #запчастидляавто #0am325025hx</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>128 800</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="n"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>не опубликовано</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="189" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Чт</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Instagram + VK</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроники</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>02E927770AL</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроник DSG6 DQ250 в сборе</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Уже с электронной платой 02E927770AL</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>• Готовый узел вместо ремонта по частям
+• Плата уже установлена
+• Для коробок DSG6 DQ250</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>photos/02E927770AL/ — 1 шт.</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроник для DSG6 DQ250 в сборе с платой — готовый узел для замены 🔧
+🔹 Готовый узел вместо ремонта по частям
+🔹 Плата уже установлена
+🔹 Для коробок DSG6 DQ250
+✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG6 DQ250 (02E)
+🔩 Артикул: 02E927770AL
+📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>#leoparts #dq250 #dsg6 #дсг6 #ремонтdq250 #02e #мехатроник #ремонтмехатроника #запчастимехатроника #tiguan #volkswagen #запчастидляакпп #автомастер #02e927770al</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>118 000</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="n"/>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>не опубликовано</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="162" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>46325</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Instagram + VK</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроники</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>0am325025x</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Новый мехатроник DQ200</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Новые соленоиды Bosch</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>• Новые соленоиды Bosch и гидроаккумулятор
+• Новые втулки, штоки, ремкомплект и прокладки
+• Продаётся без электронной платы</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>photos/0am325025x/ — 1 шт.</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>Мехатроник DQ200 с новыми соленоидами Bosch — гидравлическая часть без электронной платы ⚙️
+🔹 Новые соленоиды Bosch и гидроаккумулятор
+🔹 Новые втулки, штоки, ремкомплект и прокладки
+🔹 Продаётся без электронной платы
+✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
+🔩 Артикул: 0am325025x
+📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #seat #golf #автозапчастивналичии #ремонтавто #0am325025x</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>78 475</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="n"/>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>не начато</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>не опубликовано</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="175.5" customHeight="1">
+      <c r="A9" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B4" s="13" t="n">
-        <v>46320</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Вс</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="B9" s="13" t="n">
+        <v>46326</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Instagram + VK</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Штоки и втулки</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>0am325091e</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Усиленный шток 101 мм</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>0AM325091E · с доп. резинкой</t>
         </is>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>• Длинный шток нового образца (после 2012 года)
 • Усиленный, с дополнительной резинкой
 • Точная и стабильная работа сцепления</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>photos/0am325091e/ — 3 шт.</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>Длинный усиленный шток 101 мм для мехатроника DQ200 — для коробок нового образца 🔩
 🔹 Длинный шток нового образца (после 2012 года)
@@ -895,524 +1405,19 @@
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>#leoparts #dq200 #dsg7 #0am #дсг7 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #skoda #audi #автомастер #ремонтакпп #0am325091e</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>3 620</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>229</t>
-        </is>
-      </c>
-      <c r="Q4" s="7" t="n"/>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>не опубликовано</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="175.5" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>46321</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Пн</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Instagram + VK</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроники</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>0am325025H</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Проверен на стенде и на авто</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>• Тест на специальном стенде для DQ200
-• После сборки обкатка на дороге, не на подъёмнике
-• Для коробок 0AM / 0CW</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>photos/0am325025H/ — 6 шт.</t>
-        </is>
-      </c>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>Готовый мехатроник для DQ200 — каждый после сборки проверяем на стенде и обкатываем на автомобиле 🚗
-🔹 Тест на специальном стенде для DQ200
-🔹 После сборки обкатка на дороге, не на подъёмнике
-🔹 Для коробок 0AM / 0CW
-✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025H
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
-        <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #skoda #volkswagen #запчастидляавто #запчастиванкпп #0am325025h</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>68 800</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Q5" s="7" t="n"/>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>не опубликовано</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="175.5" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>46322</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Вт</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Instagram + VK</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроники</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>0AM927769D</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Электронная плата мехатроника</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>DSG7 DQ200 · 0AM927769D</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>• Блок управления мехатроника DSG7
-• Для Volkswagen, Audi, Skoda, Seat
-• Артикул 0AM927769D</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
-        </is>
-      </c>
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>photos/0AM927769D/ — 1 шт.</t>
-        </is>
-      </c>
-      <c r="M6" s="7" t="inlineStr">
-        <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 — блок управления вашей коробкой 🧠
-🔹 Блок управления мехатроника DSG7
-🔹 Для Volkswagen, Audi, Skoda, Seat
-🔹 Артикул 0AM927769D
-✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM927769D
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
-        </is>
-      </c>
-      <c r="N6" s="7" t="inlineStr">
-        <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #0am #dq200dsg7 #мехатроник #ремонтмехатроника #запчастимехатроника #электроннаяплата #golf #skoda #автозапчастивналичии #запчастидляавто #0am927769d</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>78 800</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>не опубликовано</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="189" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>46323</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Ср</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Instagram + VK</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроники</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>0am325025HX</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроник DQ200 в сборе с платой</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Электронная плата 0AM927769D</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>• Каждый соленоид проверен на стенде
-• Каждый мехатроник проверяется на авто после сборки
-• Плата уже установлена</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>photos/0am325025HX/ — 4 шт.</t>
-        </is>
-      </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроник в сборе с электронной платой — ставите и едете. Проверка на стенде и на авто 🔧
-🔹 Каждый соленоид проверен на стенде
-🔹 Каждый мехатроник проверяется на авто после сборки
-🔹 Плата уже установлена
-✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025HX
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #dq200dsg7 #роботдсг #мехатроник #ремонтмехатроника #запчастимехатроника #электроннаяплата #audi #vag #ремонтавто #запчастидляавто #0am325025hx</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>128 800</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr">
-        <is>
-          <t>не опубликовано</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="162" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>46324</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Чт</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Instagram + VK</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроники</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>02E927770AL</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроник DSG6 DQ250 в сборе</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Уже с электронной платой 02E927770AL</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>• Готовый узел вместо ремонта по частям
-• Плата уже установлена
-• Для коробок DSG6 DQ250</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
-        </is>
-      </c>
-      <c r="L8" s="7" t="inlineStr">
-        <is>
-          <t>photos/02E927770AL/ — 1 шт.</t>
-        </is>
-      </c>
-      <c r="M8" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроник для DSG6 DQ250 в сборе с платой — готовый узел для замены 🔧
-🔹 Готовый узел вместо ремонта по частям
-🔹 Плата уже установлена
-🔹 Для коробок DSG6 DQ250
-✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG6 DQ250 (02E)
-🔩 Артикул: 02E927770AL
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
-        </is>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>#leoparts #dq250 #dsg6 #дсг6 #ремонтdq250 #02e #мехатроник #ремонтмехатроника #запчастимехатроника #tiguan #volkswagen #запчастидляакпп #автомастер #02e927770al</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>118 000</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>не начато</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>не опубликовано</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="175.5" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>46325</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Instagram + VK</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроники</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Пост 1 слайд (+ до 2 доп. слайдов с фото)</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>0am325025x</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>Новый мехатроник DQ200</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Новые соленоиды Bosch</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>• Новые соленоиды Bosch и гидроаккумулятор
-• Новые втулки, штоки, ремкомплект и прокладки
-• Продаётся без электронной платы</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>Главное фото товара крупно на чистом фоне. Заголовок вверху, 3 пункта списком, плашка с артикулом внизу.</t>
-        </is>
-      </c>
-      <c r="L9" s="7" t="inlineStr">
-        <is>
-          <t>photos/0am325025x/ — 1 шт.</t>
-        </is>
-      </c>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>Мехатроник DQ200 с новыми соленоидами Bosch — гидравлическая часть без электронной платы ⚙️
-🔹 Новые соленоиды Bosch и гидроаккумулятор
-🔹 Новые втулки, штоки, ремкомплект и прокладки
-🔹 Продаётся без электронной платы
-✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025x
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #seat #golf #автозапчастивналичии #ремонтавто #0am325025x</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>78 475</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="Q9" s="7" t="n"/>
@@ -1424,11 +1429,6 @@
       <c r="S9" s="5" t="inlineStr">
         <is>
           <t>не опубликовано</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>да</t>
         </is>
       </c>
     </row>
@@ -1437,11 +1437,11 @@
         <v>6</v>
       </c>
       <c r="B10" s="12" t="n">
-        <v>46326</v>
+        <v>46327</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1527,11 +1527,11 @@
         <v>75</v>
       </c>
       <c r="B11" s="13" t="n">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1624,11 +1624,11 @@
         <v>64</v>
       </c>
       <c r="B12" s="13" t="n">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1721,11 +1721,11 @@
         <v>48</v>
       </c>
       <c r="B13" s="13" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1818,11 +1818,11 @@
         <v>12</v>
       </c>
       <c r="B14" s="13" t="n">
-        <v>46330</v>
+        <v>46331</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1915,11 +1915,11 @@
         <v>57</v>
       </c>
       <c r="B15" s="13" t="n">
-        <v>46331</v>
+        <v>46332</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -2012,11 +2012,11 @@
         <v>34</v>
       </c>
       <c r="B16" s="13" t="n">
-        <v>46332</v>
+        <v>46333</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -2109,11 +2109,11 @@
         <v>20</v>
       </c>
       <c r="B17" s="13" t="n">
-        <v>46333</v>
+        <v>46334</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -2206,11 +2206,11 @@
         <v>76</v>
       </c>
       <c r="B18" s="13" t="n">
-        <v>46334</v>
+        <v>46335</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -2303,11 +2303,11 @@
         <v>65</v>
       </c>
       <c r="B19" s="13" t="n">
-        <v>46335</v>
+        <v>46336</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -2400,11 +2400,11 @@
         <v>8</v>
       </c>
       <c r="B20" s="13" t="n">
-        <v>46336</v>
+        <v>46337</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -2497,11 +2497,11 @@
         <v>85</v>
       </c>
       <c r="B21" s="13" t="n">
-        <v>46337</v>
+        <v>46338</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -2594,11 +2594,11 @@
         <v>88</v>
       </c>
       <c r="B22" s="13" t="n">
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2695,11 +2695,11 @@
         <v>92</v>
       </c>
       <c r="B23" s="13" t="n">
-        <v>46339</v>
+        <v>46340</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2792,11 +2792,11 @@
         <v>11</v>
       </c>
       <c r="B24" s="12" t="n">
-        <v>46340</v>
+        <v>46341</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2882,11 +2882,11 @@
         <v>35</v>
       </c>
       <c r="B25" s="13" t="n">
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2979,11 +2979,11 @@
         <v>49</v>
       </c>
       <c r="B26" s="13" t="n">
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -3076,11 +3076,11 @@
         <v>22</v>
       </c>
       <c r="B27" s="13" t="n">
-        <v>46343</v>
+        <v>46344</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -3177,11 +3177,11 @@
         <v>77</v>
       </c>
       <c r="B28" s="13" t="n">
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -3274,11 +3274,11 @@
         <v>13</v>
       </c>
       <c r="B29" s="13" t="n">
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -3371,11 +3371,11 @@
         <v>58</v>
       </c>
       <c r="B30" s="13" t="n">
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -3468,11 +3468,11 @@
         <v>51</v>
       </c>
       <c r="B31" s="12" t="n">
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3558,11 +3558,11 @@
         <v>67</v>
       </c>
       <c r="B32" s="13" t="n">
-        <v>46348</v>
+        <v>46349</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -3655,11 +3655,11 @@
         <v>37</v>
       </c>
       <c r="B33" s="13" t="n">
-        <v>46349</v>
+        <v>46350</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -3752,11 +3752,11 @@
         <v>23</v>
       </c>
       <c r="B34" s="13" t="n">
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -3849,11 +3849,11 @@
         <v>78</v>
       </c>
       <c r="B35" s="13" t="n">
-        <v>46351</v>
+        <v>46352</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -3946,11 +3946,11 @@
         <v>50</v>
       </c>
       <c r="B36" s="13" t="n">
-        <v>46352</v>
+        <v>46353</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -4043,11 +4043,11 @@
         <v>38</v>
       </c>
       <c r="B37" s="13" t="n">
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -4140,11 +4140,11 @@
         <v>16</v>
       </c>
       <c r="B38" s="12" t="n">
-        <v>46354</v>
+        <v>46355</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4230,11 +4230,11 @@
         <v>68</v>
       </c>
       <c r="B39" s="13" t="n">
-        <v>46355</v>
+        <v>46356</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -4327,11 +4327,11 @@
         <v>24</v>
       </c>
       <c r="B40" s="13" t="n">
-        <v>46356</v>
+        <v>46357</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -4424,11 +4424,11 @@
         <v>14</v>
       </c>
       <c r="B41" s="13" t="n">
-        <v>46357</v>
+        <v>46358</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -4527,11 +4527,11 @@
         <v>59</v>
       </c>
       <c r="B42" s="13" t="n">
-        <v>46358</v>
+        <v>46359</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -4624,11 +4624,11 @@
         <v>79</v>
       </c>
       <c r="B43" s="13" t="n">
-        <v>46359</v>
+        <v>46360</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -4729,11 +4729,11 @@
         <v>39</v>
       </c>
       <c r="B44" s="13" t="n">
-        <v>46360</v>
+        <v>46361</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -4826,11 +4826,11 @@
         <v>25</v>
       </c>
       <c r="B45" s="13" t="n">
-        <v>46361</v>
+        <v>46362</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -4923,11 +4923,11 @@
         <v>69</v>
       </c>
       <c r="B46" s="13" t="n">
-        <v>46362</v>
+        <v>46363</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -5024,11 +5024,11 @@
         <v>52</v>
       </c>
       <c r="B47" s="13" t="n">
-        <v>46363</v>
+        <v>46364</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -5121,11 +5121,11 @@
         <v>9</v>
       </c>
       <c r="B48" s="13" t="n">
-        <v>46364</v>
+        <v>46365</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -5222,11 +5222,11 @@
         <v>86</v>
       </c>
       <c r="B49" s="13" t="n">
-        <v>46365</v>
+        <v>46366</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -5319,11 +5319,11 @@
         <v>89</v>
       </c>
       <c r="B50" s="13" t="n">
-        <v>46366</v>
+        <v>46367</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -5420,11 +5420,11 @@
         <v>93</v>
       </c>
       <c r="B51" s="13" t="n">
-        <v>46367</v>
+        <v>46368</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -5517,11 +5517,11 @@
         <v>21</v>
       </c>
       <c r="B52" s="12" t="n">
-        <v>46368</v>
+        <v>46369</v>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -5605,11 +5605,11 @@
         <v>46</v>
       </c>
       <c r="B53" s="12" t="n">
-        <v>46369</v>
+        <v>46370</v>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -5694,11 +5694,11 @@
         <v>91</v>
       </c>
       <c r="B54" s="13" t="n">
-        <v>46370</v>
+        <v>46371</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -5791,11 +5791,11 @@
         <v>95</v>
       </c>
       <c r="B55" s="13" t="n">
-        <v>46371</v>
+        <v>46372</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -5888,11 +5888,11 @@
         <v>40</v>
       </c>
       <c r="B56" s="13" t="n">
-        <v>46372</v>
+        <v>46373</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -5989,11 +5989,11 @@
         <v>80</v>
       </c>
       <c r="B57" s="13" t="n">
-        <v>46373</v>
+        <v>46374</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -6094,11 +6094,11 @@
         <v>15</v>
       </c>
       <c r="B58" s="13" t="n">
-        <v>46374</v>
+        <v>46375</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -6197,11 +6197,11 @@
         <v>60</v>
       </c>
       <c r="B59" s="13" t="n">
-        <v>46375</v>
+        <v>46376</v>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -6294,11 +6294,11 @@
         <v>27</v>
       </c>
       <c r="B60" s="13" t="n">
-        <v>46376</v>
+        <v>46377</v>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -6391,11 +6391,11 @@
         <v>70</v>
       </c>
       <c r="B61" s="13" t="n">
-        <v>46377</v>
+        <v>46378</v>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -6492,11 +6492,11 @@
         <v>42</v>
       </c>
       <c r="B62" s="13" t="n">
-        <v>46378</v>
+        <v>46379</v>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -6589,11 +6589,11 @@
         <v>53</v>
       </c>
       <c r="B63" s="13" t="n">
-        <v>46379</v>
+        <v>46380</v>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -6686,11 +6686,11 @@
         <v>81</v>
       </c>
       <c r="B64" s="13" t="n">
-        <v>46380</v>
+        <v>46381</v>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -6783,11 +6783,11 @@
         <v>28</v>
       </c>
       <c r="B65" s="13" t="n">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -6890,11 +6890,11 @@
         <v>26</v>
       </c>
       <c r="B66" s="12" t="n">
-        <v>46382</v>
+        <v>46383</v>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -6980,11 +6980,11 @@
         <v>43</v>
       </c>
       <c r="B67" s="13" t="n">
-        <v>46383</v>
+        <v>46384</v>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -7077,11 +7077,11 @@
         <v>72</v>
       </c>
       <c r="B68" s="13" t="n">
-        <v>46384</v>
+        <v>46385</v>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -7178,11 +7178,11 @@
         <v>82</v>
       </c>
       <c r="B69" s="13" t="n">
-        <v>46385</v>
+        <v>46386</v>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -7281,11 +7281,11 @@
         <v>17</v>
       </c>
       <c r="B70" s="13" t="n">
-        <v>46386</v>
+        <v>46387</v>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -7382,11 +7382,11 @@
         <v>62</v>
       </c>
       <c r="B71" s="13" t="n">
-        <v>46387</v>
+        <v>46388</v>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -7479,11 +7479,11 @@
         <v>56</v>
       </c>
       <c r="B72" s="12" t="n">
-        <v>46388</v>
+        <v>46389</v>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -7567,11 +7567,11 @@
         <v>29</v>
       </c>
       <c r="B73" s="13" t="n">
-        <v>46389</v>
+        <v>46390</v>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -7664,11 +7664,11 @@
         <v>54</v>
       </c>
       <c r="B74" s="13" t="n">
-        <v>46390</v>
+        <v>46391</v>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -7761,11 +7761,11 @@
         <v>44</v>
       </c>
       <c r="B75" s="13" t="n">
-        <v>46391</v>
+        <v>46392</v>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -7858,11 +7858,11 @@
         <v>73</v>
       </c>
       <c r="B76" s="13" t="n">
-        <v>46392</v>
+        <v>46393</v>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -7959,11 +7959,11 @@
         <v>10</v>
       </c>
       <c r="B77" s="13" t="n">
-        <v>46393</v>
+        <v>46394</v>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -8056,11 +8056,11 @@
         <v>87</v>
       </c>
       <c r="B78" s="13" t="n">
-        <v>46394</v>
+        <v>46395</v>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -8159,11 +8159,11 @@
         <v>90</v>
       </c>
       <c r="B79" s="13" t="n">
-        <v>46395</v>
+        <v>46396</v>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -8260,11 +8260,11 @@
         <v>31</v>
       </c>
       <c r="B80" s="12" t="n">
-        <v>46396</v>
+        <v>46397</v>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -8350,11 +8350,11 @@
         <v>94</v>
       </c>
       <c r="B81" s="13" t="n">
-        <v>46397</v>
+        <v>46398</v>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -8447,11 +8447,11 @@
         <v>83</v>
       </c>
       <c r="B82" s="13" t="n">
-        <v>46398</v>
+        <v>46399</v>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -8548,11 +8548,11 @@
         <v>30</v>
       </c>
       <c r="B83" s="13" t="n">
-        <v>46399</v>
+        <v>46400</v>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -8649,11 +8649,11 @@
         <v>45</v>
       </c>
       <c r="B84" s="13" t="n">
-        <v>46400</v>
+        <v>46401</v>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -8750,11 +8750,11 @@
         <v>18</v>
       </c>
       <c r="B85" s="13" t="n">
-        <v>46401</v>
+        <v>46402</v>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -8853,11 +8853,11 @@
         <v>63</v>
       </c>
       <c r="B86" s="13" t="n">
-        <v>46402</v>
+        <v>46403</v>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -8956,11 +8956,11 @@
         <v>55</v>
       </c>
       <c r="B87" s="13" t="n">
-        <v>46403</v>
+        <v>46404</v>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -9053,11 +9053,11 @@
         <v>74</v>
       </c>
       <c r="B88" s="13" t="n">
-        <v>46404</v>
+        <v>46405</v>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Вс</t>
+          <t>Пн</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -9154,11 +9154,11 @@
         <v>84</v>
       </c>
       <c r="B89" s="13" t="n">
-        <v>46405</v>
+        <v>46406</v>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Пн</t>
+          <t>Вт</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -9251,11 +9251,11 @@
         <v>32</v>
       </c>
       <c r="B90" s="13" t="n">
-        <v>46406</v>
+        <v>46407</v>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Вт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -9348,11 +9348,11 @@
         <v>47</v>
       </c>
       <c r="B91" s="13" t="n">
-        <v>46407</v>
+        <v>46408</v>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Ср</t>
+          <t>Чт</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -9449,11 +9449,11 @@
         <v>36</v>
       </c>
       <c r="B92" s="12" t="n">
-        <v>46410</v>
+        <v>46411</v>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -9536,11 +9536,11 @@
         <v>41</v>
       </c>
       <c r="B93" s="12" t="n">
-        <v>46424</v>
+        <v>46425</v>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -9623,11 +9623,11 @@
         <v>61</v>
       </c>
       <c r="B94" s="12" t="n">
-        <v>46438</v>
+        <v>46439</v>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -9710,11 +9710,11 @@
         <v>66</v>
       </c>
       <c r="B95" s="12" t="n">
-        <v>46452</v>
+        <v>46453</v>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -9797,11 +9797,11 @@
         <v>71</v>
       </c>
       <c r="B96" s="12" t="n">
-        <v>46466</v>
+        <v>46467</v>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Вс</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">

--- a/data/content_plan.xlsx
+++ b/data/content_plan.xlsx
@@ -794,7 +794,6 @@
 🔹 Узел толкателя вилки сцепления
 🔹 Продаётся поштучно
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0сц, salnik-shtoka-orig, salnik-shtoka-orig-v2
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -891,13 +890,12 @@
 🔹 После сборки обкатка на дороге, не на подъёмнике
 🔹 Для коробок 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025H
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #skoda #volkswagen #запчастидляавто #запчастиванкпп #0am325025h</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #роботдсг #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #skoda #volkswagen #запчастидляавто #запчастиванкпп</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -991,9 +989,9 @@
           <t>Электронная плата мехатроника DSG7 DQ200 — блок управления вашей коробкой 🧠
 🔹 Блок управления мехатроника DSG7
 🔹 Для Volkswagen, Audi, Skoda, Seat
-🔹 Артикул 0AM927769D
+🔹 Номер детали 0AM927769D
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM927769D
+🔩 Номер детали: 0AM927769D
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -1095,13 +1093,12 @@
 🔹 Каждый мехатроник проверяется на авто после сборки
 🔹 Плата уже установлена
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025HX
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #dq200dsg7 #роботдсг #мехатроник #ремонтмехатроника #запчастимехатроника #электроннаяплата #audi #vag #ремонтавто #запчастидляавто #0am325025hx</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #dq200dsg7 #роботдсг #мехатроник #ремонтмехатроника #запчастимехатроника #электроннаяплата #audi #vag #ремонтавто #запчастидляавто</t>
         </is>
       </c>
       <c r="O6" s="5" t="inlineStr">
@@ -1197,7 +1194,7 @@
 🔹 Плата уже установлена
 🔹 Для коробок DSG6 DQ250
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG6 DQ250 (02E)
-🔩 Артикул: 02E927770AL
+🔩 Номер детали: 02E927770AL
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -1299,13 +1296,12 @@
 🔹 Новые втулки, штоки, ремкомплект и прокладки
 🔹 Продаётся без электронной платы
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025x
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #seat #golf #автозапчастивналичии #ремонтавто #0am325025x</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0cw #ремонтdq200 #мехатроник #ремонтмехатроника #запчастимехатроника #seat #golf #автозапчастивналичии #ремонтавто</t>
         </is>
       </c>
       <c r="O8" s="5" t="inlineStr">
@@ -1401,7 +1397,7 @@
 🔹 Усиленный, с дополнительной резинкой
 🔹 Точная и стабильная работа сцепления
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325091e
+🔩 Номер детали: 0AM325091E
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -1588,7 +1584,7 @@
 🔹 Новый, в наличии
 🔹 Соленоиды продаются и комплектом
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM325025B
+🔩 Номер детали: 0AM325025B
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -1685,7 +1681,7 @@
 🔹 Заметна разница с дешёвыми аналогами
 🔹 Для мехатроника DQ200 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM325433E
+🔩 Номер детали: 0AM325433E
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -1780,9 +1776,9 @@
           <t>Сальник толкателя вилки мехатроника DQ200 — новый, в наличии 💧
 🔹 Новый, отличное качество
 🔹 Для мехатроника DQ200 0AM / 0CW
-🔹 Артикул 0AM325413A
+🔹 Номер детали 0AM325413A
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM325413A
+🔩 Номер детали: 0AM325413A
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -1877,9 +1873,9 @@
           <t>Усиленная алюминиевая гидроплита для мехатроника DQ200 — утолщённая стенка для большего ресурса 💪
 🔹 Увеличенный ресурс
 🔹 Защита от трещин и ошибок
-🔹 Артикул 0AM325066AE
+🔹 Номер детали 0AM325066AE
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325066ae
+🔩 Номер детали: 0AM325066AE
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -1976,7 +1972,7 @@
 🔹 Защищает от загрязнений и утечек
 🔹 Для коробок 0AM и 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM325219C
+🔩 Номер детали: 0AM325219C
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -2073,7 +2069,6 @@
 🔹 Герметичнее аналогов
 🔹 Меньше риск повторной течи
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: salniki-shtokov-orig
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -2170,7 +2165,7 @@
 🔹 Усиленный, с дополнительной резинкой
 🔹 Точная передача усилия на сцепление
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325091f
+🔩 Номер детали: 0AM325091F
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -2265,9 +2260,9 @@
           <t>Новый соленоид переключения Shift (BOSCH) для мехатроника DQ200 ⚡
 🔹 Новый, отличное качество
 🔹 Для мехатроника DQ200 0AM / 0CW
-🔹 Артикул 0am325025n
+🔹 Номер детали 0AM325025N
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025n
+🔩 Номер детали: 0AM325025N
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -2364,7 +2359,6 @@
 🔹 Для ремонта гидроблока
 🔹 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: filtr-dsg7-dq200
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -2461,7 +2455,7 @@
 🔹 Плита мехатроника, сальники и уплотнения
 🔹 Для восстановления и обслуживания DQ200
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025
+🔩 Номер детали: 0AM325025
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -2558,7 +2552,7 @@
 🔹 Новые, отличное качество
 🔹 Для DSG7 DQ200 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM927769N
+🔩 Номер детали: 0AM927769N
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -2659,7 +2653,7 @@
 🔹 Транспортная заглушка мехатроника 0AM325120A
 🔹 Новые, отличное качество
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM301212A, 0AM325120A
+🔩 Номер детали: 0AM301212A, 0AM325120A
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -2756,13 +2750,12 @@
 🔹 Крышка, колба, корпус обратного клапана
 🔹 Для 1.8 TSI и 2.0 TSI
 ✅ Подходит: Двигатели VAG EA888 Gen3 · 1.8 TSI и 2.0 TSI
-🔩 Артикул: EA888
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #ea888 #ea888gen3 #18tsi #двигательea888 #масляныйфильтр #корпусфильтра #volkswagen #octavia #запчастидляакпп #запчастиванкпп</t>
+          <t>#leoparts #ea888gen3 #18tsi #двигательea888 #масляныйфильтр #корпусфильтра #volkswagen #octavia #запчастидляакпп #запчастиванкпп</t>
         </is>
       </c>
       <c r="O23" s="5" t="inlineStr">
@@ -2943,7 +2936,6 @@
 🔹 Устраняет течь с обеих сторон
 🔹 DSG7 DQ200
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: salniki-shtokov-2sht
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -3040,7 +3032,6 @@
 🔹 4 шт в комплекте
 🔹 Без поршней, только сальники
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: salniki-tolkatelya-4sht
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -3141,13 +3132,12 @@
 🔹 2 усиленных штока + 2 новые втулки
 🔹 Один заказ вместо четырёх
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325091e-set, 0am325091f-set
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #0am #мехатроникdq200 #шток #штокмехатроника #усиленныйшток #втулкиштоков #golf #audi #запчастидляакпп #ремонтавто #0am325091eset</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #0am #мехатроникdq200 #шток #штокмехатроника #усиленныйшток #втулкиштоков #golf #audi #запчастидляакпп #ремонтавто</t>
         </is>
       </c>
       <c r="O27" s="5" t="inlineStr">
@@ -3236,9 +3226,9 @@
           <t>Оригинальная сепараторная пластина VAG под плиту мехатроника DQ200 🔧
 🔹 Под плиту мехатроника
 🔹 Оригинал, отличное качество
-🔹 Артикул 0AM325467J
+🔹 Номер детали 0AM325467J
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM325467J
+🔩 Номер детали: 0AM325467J
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -3335,7 +3325,6 @@
 🔹 Снижает риск деформации каналов
 🔹 Ставится вместе с гидроплитой при капремонте
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: stalnaya-vstavka-plity
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -3432,7 +3421,7 @@
 🔹 Герметичность при ремонте
 🔹 Для VW, Audi, Skoda, Seat
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM325443D
+🔩 Номер детали: 0AM325443D
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -3617,9 +3606,9 @@
           <t>Масляный фильтр для коробки DSG6 DQ250 — замена при обслуживании 🔧
 🔹 Отличное качество
 🔹 Для коробки DSG6 DQ250
-🔹 Артикул 02E305051C
+🔹 Номер детали 02E305051C
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG6 DQ250 (02E)
-🔩 Артикул: 02E305051C
+🔩 Номер детали: 02E305051C
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -3714,9 +3703,9 @@
           <t>Манжета-сальник штока мехатроника DQ200 — расходник, который стоит менять при любом вскрытии 🔧
 🔹 Новый, отличный материал манжеты
 🔹 Для мехатроника DQ200 0AM / 0CW
-🔹 Артикул 0AM325066AD
+🔹 Номер детали 0AM325066AD
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325066ad
+🔩 Номер детали: 0AM325066AD
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -3813,13 +3802,12 @@
 🔹 Новая втулка (гильза) в комплекте
 🔹 Усиленные штоки ходят дольше обычных
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025u
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #роботдсг #0am #шток #штокмехатроника #усиленныйшток #втулкиштоков #polo #seat #автозапчастивналичии #запчастидляакпп #0am325025u</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #роботдсг #0am #шток #штокмехатроника #усиленныйшток #втулкиштоков #polo #seat #автозапчастивналичии #запчастидляакпп</t>
         </is>
       </c>
       <c r="O34" s="5" t="inlineStr">
@@ -3910,7 +3898,6 @@
 🔹 Новая, с завода
 🔹 Отправка в день заказа
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: separatornaya-plastina-dq200
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -4007,7 +3994,6 @@
 🔹 Гальваническое покрытие
 🔹 Комплект на все толкатели
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: salnik-tolkatelya-alum
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -4104,13 +4090,12 @@
 🔹 Восстанавливает герметичность узла сцепления
 🔹 Защита штока от грязи
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 122390AKAF
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #мехатроникdq200 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #пыльник #golf #polo #запчастиванкпп #автозапчастивналичии #122390akaf</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #мехатроникdq200 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #пыльник #golf #polo #запчастиванкпп #автозапчастивналичии</t>
         </is>
       </c>
       <c r="O37" s="5" t="inlineStr">
@@ -4291,7 +4276,6 @@
 🔹 Ставится в корпус фильтра
 🔹 Корпус — отдельная позиция
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ500 (0BH)
-🔩 Артикул: filtr-dsg7-dq500
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -4388,13 +4372,12 @@
 🔹 Новая втулка (гильза) в комплекте
 🔹 Устраняет задиры и износ в узле
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025z
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #мехатроникdq200 #дсг7 #шток #штокмехатроника #усиленныйшток #втулкиштоков #skoda #audi #запчастидляакпп #автомастер #0am325025z</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #мехатроникdq200 #дсг7 #шток #штокмехатроника #усиленныйшток #втулкиштоков #skoda #audi #запчастидляакпп #автомастер</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
@@ -4491,7 +4474,6 @@
 🔹 Масляный фильтр (в одном варианте улучшенный)
 🔹 Всё в одном заказе
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: plita-filtr-orig, plita-filtr, plita-filtr-v2
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -4588,13 +4570,12 @@
 🔹 Усиленная прокладка
 🔹 Исключает утечки масла после обслуживания
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025ae
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0am #0cw #прокладка #прокладкамехатроника #крышкамехатроника #крышкаштока #vag #volkswagen #автомастер #автосервис #0am325025ae</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0am #0cw #прокладка #прокладкамехатроника #крышкамехатроника #крышкаштока #vag #volkswagen #автомастер #автосервис</t>
         </is>
       </c>
       <c r="O42" s="5" t="inlineStr">
@@ -4689,13 +4670,12 @@
 🔹 Новые, с завода
 🔹 Есть и оригинальный вариант
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: separatornaya-plastiny-solenoid-dq200, 0am325025j
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #роботдсг #0cw #соленоиды #соленоидыdsg #сепараторнаяпластина #пластинысоленоидов #golf #polo #запчастидляавто #автозапчасти #0am325025j</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #роботдсг #0cw #соленоиды #соленоидыdsg #сепараторнаяпластина #пластинысоленоидов #golf #polo #запчастидляавто #автозапчасти</t>
         </is>
       </c>
       <c r="O43" s="5" t="inlineStr">
@@ -4790,13 +4770,12 @@
 🔹 Для мехатроника DQ200 0AM / 0CW
 🔹 122390AK-AF
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 122390AK-AF
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw #0am #шток #штокмехатроника #усиленныйшток #пыльник #polo #volkswagen #запчастиванкпп #автосервис #122390akaf</t>
+          <t>#leoparts #dq200 #dsg7 #ремонтdq200 #0cw #0am #шток #штокмехатроника #усиленныйшток #пыльник #polo #volkswagen #запчастиванкпп #автосервис</t>
         </is>
       </c>
       <c r="O44" s="5" t="inlineStr">
@@ -4887,7 +4866,7 @@
 🔹 Точный ход без боковых люфтов
 🔹 Новая втулка — на новый шток
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025D
+🔩 Номер детали: 0AM325025D
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -4988,7 +4967,7 @@
 🔹 Улучшенный отвод тепла, ниже температура масла
 🔹 Резиновое кольцо в комплекте
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG6 DQ250 (02E)
-🔩 Артикул: 02e305045, 02E 305 045
+🔩 Номер детали: 02E305045, 02E305045
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -5085,7 +5064,6 @@
 🔹 4 сальника толкателей
 🔹 Всё в одном заказе
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: tolkateli-4-salniki-4
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -5186,13 +5164,12 @@
 🔹 Оригинальные сальники и пыльники (Германия)
 🔹 Для капитального ремонта мехатроника
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0cw0am325025, Dq200dsg70am0cw
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0am #ремонтdq200 #ремкомплект #ремкомплектмехатроника #volkswagen #polo #запчастиванкпп #автозапчастивналичии #0cw0am325025</t>
+          <t>#leoparts #dq200 #dsg7 #мехатроникdq200 #0am #ремонтdq200 #ремкомплект #ремкомплектмехатроника #volkswagen #polo #запчастиванкпп #автозапчастивналичии</t>
         </is>
       </c>
       <c r="O48" s="5" t="inlineStr">
@@ -5283,13 +5260,12 @@
 🔹 Расходный элемент при ремонте
 🔹 Для DSG7 DQ200 0AM
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0cw325025h
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #мехатроникdq200 #роботдсг #прокладка #прокладкамехатроника #электроннаяплата #блокуправленияdsg #seat #octavia #запчастидляакпп #запчастидляавто #0cw325025h</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #мехатроникdq200 #роботдсг #прокладка #прокладкамехатроника #электроннаяплата #блокуправленияdsg #seat #octavia #запчастидляакпп #запчастидляавто</t>
         </is>
       </c>
       <c r="O49" s="5" t="inlineStr">
@@ -5384,7 +5360,6 @@
 🔹 Меняются при течи с соответствующей стороны
 🔹 DSG7 DQ200
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: salnikprivod-l, salnikprivod-r
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -5481,13 +5456,12 @@
 🔹 Удерживает масло в системе при остановке
 🔹 Для 1.8 TSI и 2.0 TSI
 ✅ Подходит: Двигатели VAG EA888 Gen3 · 1.8 TSI и 2.0 TSI
-🔩 Артикул: Ea888gen3
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #ea888 #ea888gen3 #20tsi #tsi #18tsi #масляныйфильтр #корпусфильтра #обратныйклапан #octavia #passat #ремонтакпп #автозапчастивналичии</t>
+          <t>#leoparts #ea888 #20tsi #tsi #18tsi #масляныйфильтр #корпусфильтра #обратныйклапан #octavia #passat #ремонтакпп #автозапчастивналичии</t>
         </is>
       </c>
       <c r="O51" s="5" t="inlineStr">
@@ -5755,7 +5729,7 @@
 🔹 Корректная работа трансмиссии
 🔹 Для ремонта вариаторов Nissan, Renault, Mitsubishi
 ✅ Подходит: Nissan, Renault, Mitsubishi · CVT JF015E (RE0F11A)
-🔩 Артикул: 317053TX0C
+🔩 Номер детали: 317053TX0C
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -5852,7 +5826,7 @@
 🔹 Работает с датчиком положения распредвала
 🔹 GM 55565480
 ✅ Подходит: GM · 55565480 (5636119)
-🔩 Артикул: 55565480
+🔩 Номер детали: 55565480
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -5953,7 +5927,6 @@
 🔹 Плотнее прилегают и служат дольше аналогов
 🔹 Комплект на 2 штока
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: pylniki-shtokov-orig, pylniki-shtokov-orig-v2
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -6054,7 +6027,6 @@
 🔹 Новые, с завода
 🔹 Отправка в день заказа
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: plastina-solenoid-dq200, plastiny-solenoid-dq200-2sht
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -6161,7 +6133,6 @@
 🔹 То же с оригинальными пыльниками VW
 🔹 Плита + фильтр + 2 оригинальных сальника VW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: plita-filtr-pylniki, plita-filtr-pylniki-orig, plita-filtr-salniki-orig
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -6258,7 +6229,6 @@
 🔹 Защита от загрязнений
 🔹 Против подтёков масла
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: kryshka-mehatronika-dq200
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -6355,7 +6325,6 @@
 🔹 Меняются парой со штоками
 🔹 Новые втулки без новых штоков проблему не решают
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: vtulki-shtokov-2sht
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -6456,13 +6425,13 @@
 🔹 Лучше отводит тепло, снижает температуру масла
 🔹 Резиновое кольцо в комплекте
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ500 (0BH)
-🔩 Артикул: 0BH325183, 0BH325183 B
+🔩 Номер детали: 0BH325183B
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq500 #dsg7 #dq500dsg7 #ремонтdq500 #дсг7 #фильтрdsg #масляныйфильтр #корпусфильтра #skoda #volkswagen #автомастер #ремонтакпп #0bh325183</t>
+          <t>#leoparts #dq500 #dsg7 #dq500dsg7 #ремонтdq500 #дсг7 #фильтрdsg #масляныйфильтр #корпусфильтра #skoda #volkswagen #автомастер #ремонтакпп</t>
         </is>
       </c>
       <c r="O61" s="5" t="inlineStr">
@@ -6551,9 +6520,9 @@
           <t>Крышка штока мехатроника DQ200 — небольшая деталь, которая держит узел в порядке 🔩
 🔹 Новая, отличное качество
 🔹 Для мехатроника 0AM / 0CW
-🔹 Артикул 0AM325025Q
+🔹 Номер детали 0AM325025Q
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025q
+🔩 Номер детали: 0AM325025Q
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -6650,7 +6619,6 @@
 🔹 4 штатных сальника
 🔹 4 усиленных алюминиевых сальника
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: tolkateli-salniki-alum-komplekt
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -6747,7 +6715,6 @@
 🔹 Сепараторная пластина — отдельно (0AM325467J)
 🔹 Для 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: plastiny-solenoid-orig
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -6850,7 +6817,6 @@
 🔹 Предотвращают потерю давления
 🔹 Комплект 2 кольца или по одному
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: prokladka-vtulki-dq200, prokladka-vtulki-verh-dq200, prokladka-vtulki-niz-dq200
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -7039,15 +7005,13 @@
           <t>Ремкомплект на два штока одним набором: пыльники, сальники и крышки 📦
 🔹 Всё для обновления обоих штоков
 🔹 Новые материалы, отличное качество
-🔹 Артикул 0am325025G
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025G
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #дсг7 #dq200dsg7 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #ремкомплект #seat #vag #автозапчастивналичии #запчастидляавто #0am325025g</t>
+          <t>#leoparts #dq200 #dsg7 #дсг7 #dq200dsg7 #ремонтdq200 #шток #штокмехатроника #усиленныйшток #ремкомплект #seat #vag #автозапчастивналичии #запчастидляавто</t>
         </is>
       </c>
       <c r="O67" s="5" t="inlineStr">
@@ -7142,13 +7106,12 @@
 🔹 Улучшенный отвод тепла
 🔹 Снижает температуру масла
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ500 (0BH)
-🔩 Артикул: DQ500, Dq500
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq500 #dsg7 #дсг7 #0bh #мокроесцепление #фильтрdsg #масляныйфильтр #корпусфильтра #volkswagen #passat #автомастер #автозапчастивналичии</t>
+          <t>#leoparts #dsg7 #дсг7 #0bh #мокроесцепление #фильтрdsg #масляныйфильтр #корпусфильтра #volkswagen #passat #автомастер #автозапчастивналичии</t>
         </is>
       </c>
       <c r="O68" s="5" t="inlineStr">
@@ -7245,7 +7208,7 @@
 🔹 Одна планка крепит 4 соленоида одной стороны
 🔹 Планка 1 шт или комплект 2 шт
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325477ae, 0am325477, planka-solenoid-2sht
+🔩 Номер детали: 0AM325477AE
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -7346,7 +7309,6 @@
 🔹 Вариант с обычными деталями
 🔹 Вариант с оригинальными (VAG) пыльниками и сальниками
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: plita-filtr-pylniki-sal, plita-filtr-pylniki-sal-orig
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -7443,7 +7405,6 @@
 🔹 Предотвращает подтёки масла
 🔹 Новая, отправка в день заказа
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: prokladka-kryshki-dq200
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -7628,7 +7589,7 @@
 🔹 Усиленное исполнение
 🔹 Точная и стабильная работа
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325066AC
+🔩 Номер детали: 0AM325066AC
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -7725,7 +7686,7 @@
 🔹 Усиленное исполнение
 🔹 Отличное качество
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025r
+🔩 Номер детали: 0AM325025R
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -7822,13 +7783,12 @@
 🔹 Подходит под короткий и длинный шток
 🔹 Комплект: сальник, пыльник, крышка
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025hfe
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200 #0cw #шток #штокмехатроника #усиленныйшток #ремкомплект #octavia #volkswagen #ремонтакпп #ремонтавто #0am325025hfe</t>
+          <t>#leoparts #dq200 #dsg7 #роботдсг #ремонтdq200 #0cw #шток #штокмехатроника #усиленныйшток #ремкомплект #octavia #volkswagen #ремонтакпп #ремонтавто</t>
         </is>
       </c>
       <c r="O75" s="5" t="inlineStr">
@@ -7919,7 +7879,6 @@
 🔹 Для тех, у кого треснул или потерян корпус
 🔹 Volkswagen, Škoda, Audi, Seat, Porsche
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat, Porsche · DSG7 DQ500 (0BH)
-🔩 Артикул: korpus-filtra-0bh325159
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -8020,7 +7979,7 @@
 🔹 Сепараторные пластины
 🔹 Уплотнения для сборки после ремонта
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025m
+🔩 Номер детали: 0AM325025M
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -8123,13 +8082,12 @@
 🔹 Уплотнение электромотора гидроблока
 🔹 Уплотнение насоса гидроблока
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0cw0am, 0cw0amdsgdq200, Dq200dsg7
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #0cw #0am #ремонтdq200 #уплотнение #прокладка #skoda #volkswagen #автозапчасти #запчастидляакпп #0cw0amdsgdq200</t>
+          <t>#leoparts #dq200 #dsg7 #0cw #0am #ремонтdq200 #уплотнение #прокладка #skoda #volkswagen #автозапчасти #запчастидляакпп</t>
         </is>
       </c>
       <c r="O78" s="5" t="inlineStr">
@@ -8224,7 +8182,6 @@
 🔹 Выходной вал — вторичный вал коробки
 🔹 Меняются при течи масла в этой зоне
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: salnikvhod, salnikvihod
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -8411,13 +8368,12 @@
 🔹 Обратный клапан масляного фильтра
 🔹 Комплектом выгоднее, чем по отдельности
 ✅ Подходит: Двигатели VAG EA888 Gen3 · 1.8 TSI и 2.0 TSI
-🔩 Артикул: EA888gen3
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #ea888 #ea888gen3 #tsi #двигательea888 #масляныйфильтр #обратныйклапан #tiguan #skoda #запчастидляавто #автозапчасти</t>
+          <t>#leoparts #ea888 #tsi #двигательea888 #масляныйфильтр #обратныйклапан #tiguan #skoda #запчастидляавто #автозапчасти</t>
         </is>
       </c>
       <c r="O81" s="5" t="inlineStr">
@@ -8512,7 +8468,7 @@
 🔹 Поддерживает давление в системе
 🔹 Есть восстановленный оригинал VAG
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0AM325587E, gidroakkumulyator-orig
+🔩 Номер детали: 0AM325587E
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -8613,7 +8569,6 @@
 🔹 2 пыльника и 2 крышки
 🔹 Для мехатроников 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: porshni-usil-pylniki-kryshki, porshni-usil-pylniki-kryshki-v2
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -8714,7 +8669,6 @@
 🔹 Комплект на 2 штока полностью
 🔹 Для мехатроников 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: remkomplekt-shtokov-orig, remkomplekt-shtokov-orig-v2
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -8817,7 +8771,6 @@
 🔹 2 пыльника + 2 сальника штоков
 🔹 Есть вариант с оригинальными (VAG) пыльниками и сальниками
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: plita-pylniki-salniki, plita-pylniki-salniki-orig, plita-pylniki-salniki-orig-v2
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -8920,7 +8873,7 @@
 🔹 Длинный M8×90 (WHT001922)
 🔹 Набор: 4 длинных + 3 коротких
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 01X301127C, WHT001922, 0am325025f
+🔩 Номер детали: 01X301127C, WHT001922
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -9017,7 +8970,6 @@
 🔹 Поэтому подшипник один
 🔹 Для DQ200 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: podshipnik-vilki-6
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -9118,7 +9070,6 @@
 🔹 Защищает соленоиды от загрязнений
 🔹 Аналог 123014AF и оригинальный вариант
 ✅ Подходит: Audi Q5, A4, A5 и другие · DSG7 0B5 (DL501) / DQ500 (0BH)
-🔩 Артикул: 123014‑AF, filtr-setka-0b5-orig
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -9215,13 +9166,12 @@
 🔹 Всегда в наличии
 🔹 Для мехатроника 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025С
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr">
         <is>
-          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #дсг7 #роботдсг #гидроаккумулятор #уплотнительноекольцо #golf #polo #запчастидляакпп #автозапчасти #0am325025с</t>
+          <t>#leoparts #dq200 #dsg7 #dq200dsg7 #дсг7 #роботдсг #гидроаккумулятор #уплотнительноекольцо #golf #polo #запчастидляакпп #автозапчасти</t>
         </is>
       </c>
       <c r="O89" s="5" t="inlineStr">
@@ -9312,7 +9262,7 @@
 🔹 Новый, отличное качество
 🔹 Для мехатроника DQ200 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025l
+🔩 Номер детали: 0AM325025L
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
@@ -9413,7 +9363,7 @@
 🔹 Мелкие детали часто ломаются при разборке
 🔹 Одна клипса или комплект 2 шт
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-🔩 Артикул: 0am325025P, klipsy-shtokov-2sht
+🔩 Номер детали: 0AM325025P
 📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>

--- a/data/content_plan.xlsx
+++ b/data/content_plan.xlsx
@@ -683,7 +683,7 @@
           <t>Обложка: логотип Leo.Parts + «Запчасти для DSG и ремонта мехатроников»
 Что у нас есть: мехатроники, ремкомплекты, гидроплиты, штоки, сальники, фильтры, соленоиды
 Для кого: автосервисы и частные мастера, ремонтирующие DSG
-Где купить: Ozon, Wildberries, Авито, сайт
+Где купить: Ozon, Wildberries, Яндекс Маркет, сайт
 Слайд-призыв: «Пишите — подскажем по подбору»</t>
         </is>
       </c>
@@ -698,9 +698,9 @@
 Продаём запчасти для коробок DSG: мехатроники, ремкомплекты, гидроплиты, штоки, сальники, фильтры, соленоиды и многое другое. В основном DSG7 DQ200, а также DQ250, DQ500, 0B5 и вариаторы.
 📦 Новые детали и оригинал VAG
 🔧 Для автосервисов и частных мастеров
-🛒 Ozon, Wildberries, Авито и сайт — ссылки в шапке профиля
+🛒 Ozon, Wildberries, Яндекс Маркет и сайт — ссылки в шапке профиля
 В ближайшие недели покажем весь каталог. Подписывайтесь, чтобы не потерять нужную деталь 🔔
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N2" s="4" t="inlineStr">
@@ -794,7 +794,7 @@
 🔹 Узел толкателя вилки сцепления
 🔹 Продаётся поштучно
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
@@ -890,7 +890,7 @@
 🔹 После сборки обкатка на дороге, не на подъёмнике
 🔹 Для коробок 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N4" s="7" t="inlineStr">
@@ -992,7 +992,7 @@
 🔹 Номер детали 0AM927769D
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM927769D
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -1093,7 +1093,7 @@
 🔹 Каждый мехатроник проверяется на авто после сборки
 🔹 Плата уже установлена
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N6" s="7" t="inlineStr">
@@ -1195,7 +1195,7 @@
 🔹 Для коробок DSG6 DQ250
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG6 DQ250 (02E)
 🔩 Номер детали: 02E927770AL
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -1296,7 +1296,7 @@
 🔹 Новые втулки, штоки, ремкомплект и прокладки
 🔹 Продаётся без электронной платы
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
@@ -1398,7 +1398,7 @@
 🔹 Точная и стабильная работа сцепления
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325091E
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N9" s="7" t="inlineStr">
@@ -1496,7 +1496,7 @@
 Чаще всего изнашиваются сальники, пыльники, штоки и втулки — их можно заменить отдельно, не меняя весь узел.
 В карусели — как устроен мехатроник. Сохраните, чтобы не потерять 💾
 В нашем каталоге есть и детали, и готовые мехатроники — смотрите ссылки в шапке профиля.
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1585,7 +1585,7 @@
 🔹 Соленоиды продаются и комплектом
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325025B
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N11" s="7" t="inlineStr">
@@ -1682,7 +1682,7 @@
 🔹 Для мехатроника DQ200 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325433E
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N12" s="7" t="inlineStr">
@@ -1779,7 +1779,7 @@
 🔹 Номер детали 0AM325413A
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325413A
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N13" s="7" t="inlineStr">
@@ -1876,7 +1876,7 @@
 🔹 Номер детали 0AM325066AE
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325066AE
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
@@ -1973,7 +1973,7 @@
 🔹 Для коробок 0AM и 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325219C
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
@@ -2069,7 +2069,7 @@
 🔹 Герметичнее аналогов
 🔹 Меньше риск повторной течи
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
@@ -2166,7 +2166,7 @@
 🔹 Точная передача усилия на сцепление
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325091F
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
@@ -2263,7 +2263,7 @@
 🔹 Номер детали 0AM325025N
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325025N
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
@@ -2359,7 +2359,7 @@
 🔹 Для ремонта гидроблока
 🔹 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
@@ -2456,7 +2456,7 @@
 🔹 Для восстановления и обслуживания DQ200
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325025
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
@@ -2553,7 +2553,7 @@
 🔹 Для DSG7 DQ200 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM927769N
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
@@ -2654,7 +2654,7 @@
 🔹 Новые, отличное качество
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM301212A, 0AM325120A
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
@@ -2750,7 +2750,7 @@
 🔹 Крышка, колба, корпус обратного клапана
 🔹 Для 1.8 TSI и 2.0 TSI
 ✅ Подходит: Двигатели VAG EA888 Gen3 · 1.8 TSI и 2.0 TSI
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
@@ -2848,7 +2848,7 @@
 🔹 DQ250 (DSG6, 02E) — 6 ступеней, мокрое сцепление
 🔹 DQ500 (DSG7, 0BH) — 7 ступеней, мокрое сцепление
 Детали между ними не взаимозаменяемы, поэтому перед заказом сверьте код коробки. Не уверены — напишите нам, подскажем.
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2936,7 +2936,7 @@
 🔹 Устраняет течь с обеих сторон
 🔹 DSG7 DQ200
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
@@ -3032,7 +3032,7 @@
 🔹 4 шт в комплекте
 🔹 Без поршней, только сальники
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
@@ -3132,7 +3132,7 @@
 🔹 2 усиленных штока + 2 новые втулки
 🔹 Один заказ вместо четырёх
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
@@ -3229,7 +3229,7 @@
 🔹 Номер детали 0AM325467J
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325467J
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
@@ -3325,7 +3325,7 @@
 🔹 Снижает риск деформации каналов
 🔹 Ставится вместе с гидроплитой при капремонте
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
@@ -3422,7 +3422,7 @@
 🔹 Для VW, Audi, Skoda, Seat
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325443D
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N30" s="7" t="inlineStr">
@@ -3502,7 +3502,7 @@
       <c r="K31" s="4" t="inlineStr">
         <is>
           <t>Обложка: «Частые вопросы»
-Где заказать: Ozon, Wildberries, Авито, сайт
+Где заказать: Ozon, Wildberries, Яндекс Маркет, сайт
 Сроки отправки: [уточнить у владельца]
 Гарантия и возврат: [уточнить у владельца]
 Связь: сообщения профиля</t>
@@ -3516,11 +3516,11 @@
       <c r="M31" s="4" t="inlineStr">
         <is>
           <t>Отвечаем на частые вопросы 💬
-🛒 Заказать можно на Ozon, Wildberries, Авито и на нашем сайте
+🛒 Заказать можно на Ozon, Wildberries, Яндекс Маркете и на нашем сайте
 📦 Многие позиции отправляем в день заказа
 📩 Если не уверены в подборе — напишите нам
 [Владелец: уточнить сроки отправки и условия возврата перед публикацией]
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
@@ -3609,7 +3609,7 @@
 🔹 Номер детали 02E305051C
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG6 DQ250 (02E)
 🔩 Номер детали: 02E305051C
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
@@ -3706,7 +3706,7 @@
 🔹 Номер детали 0AM325066AD
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325066AD
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N33" s="7" t="inlineStr">
@@ -3802,7 +3802,7 @@
 🔹 Новая втулка (гильза) в комплекте
 🔹 Усиленные штоки ходят дольше обычных
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N34" s="7" t="inlineStr">
@@ -3898,7 +3898,7 @@
 🔹 Новая, с завода
 🔹 Отправка в день заказа
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N35" s="7" t="inlineStr">
@@ -3994,7 +3994,7 @@
 🔹 Гальваническое покрытие
 🔹 Комплект на все толкатели
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
@@ -4090,7 +4090,7 @@
 🔹 Восстанавливает герметичность узла сцепления
 🔹 Защита штока от грязи
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
@@ -4188,7 +4188,7 @@
 2️⃣ Сверьте артикул детали с тем, что на старой
 3️⃣ Для штоков проверьте длину: 101 мм или 99 мм
 Не уверены — пришлите нам код и фото, поможем подобрать 📩
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
@@ -4276,7 +4276,7 @@
 🔹 Ставится в корпус фильтра
 🔹 Корпус — отдельная позиция
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ500 (0BH)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N39" s="7" t="inlineStr">
@@ -4372,7 +4372,7 @@
 🔹 Новая втулка (гильза) в комплекте
 🔹 Устраняет задиры и износ в узле
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
@@ -4474,7 +4474,7 @@
 🔹 Масляный фильтр (в одном варианте улучшенный)
 🔹 Всё в одном заказе
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N41" s="7" t="inlineStr">
@@ -4570,7 +4570,7 @@
 🔹 Усиленная прокладка
 🔹 Исключает утечки масла после обслуживания
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
@@ -4670,7 +4670,7 @@
 🔹 Новые, с завода
 🔹 Есть и оригинальный вариант
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N43" s="7" t="inlineStr">
@@ -4770,7 +4770,7 @@
 🔹 Для мехатроника DQ200 0AM / 0CW
 🔹 122390AK-AF
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
@@ -4867,7 +4867,7 @@
 🔹 Новая втулка — на новый шток
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325025D
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
@@ -4968,7 +4968,7 @@
 🔹 Резиновое кольцо в комплекте
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG6 DQ250 (02E)
 🔩 Номер детали: 02E305045, 02E305045
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
@@ -5064,7 +5064,7 @@
 🔹 4 сальника толкателей
 🔹 Всё в одном заказе
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
@@ -5164,7 +5164,7 @@
 🔹 Оригинальные сальники и пыльники (Германия)
 🔹 Для капитального ремонта мехатроника
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
@@ -5260,7 +5260,7 @@
 🔹 Расходный элемент при ремонте
 🔹 Для DSG7 DQ200 0AM
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
@@ -5360,7 +5360,7 @@
 🔹 Меняются при течи с соответствующей стороны
 🔹 DSG7 DQ200
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
@@ -5456,7 +5456,7 @@
 🔹 Удерживает масло в системе при остановке
 🔹 Для 1.8 TSI и 2.0 TSI
 ✅ Подходит: Двигатели VAG EA888 Gen3 · 1.8 TSI и 2.0 TSI
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N51" s="7" t="inlineStr">
@@ -5552,7 +5552,7 @@
           <t>Подтёки масла в зоне штоков мехатроника — частая проблема DQ200 💧
 Чаще всего причина в изношенных сальниках, пыльниках и крышках штоков. Устранить её можно ремкомплектом штока без полной разборки мехатроника, а при более сильном износе — ремкомплектом на два штока и новыми втулками.
 Подобрать комплект — в карусели и в нашем каталоге 👆
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5641,7 +5641,7 @@
 1️⃣ Каждый соленоид — на специализированном стенде
 2️⃣ Собранный мехатроник — на автомобиле: не на подъёмнике, а в реальной обкатке на дороге
 Так мы видим то, что на стенде не заметно. Мехатроники — в каталоге по ссылкам в шапке профиля.
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -5730,7 +5730,7 @@
 🔹 Для ремонта вариаторов Nissan, Renault, Mitsubishi
 ✅ Подходит: Nissan, Renault, Mitsubishi · CVT JF015E (RE0F11A)
 🔩 Номер детали: 317053TX0C
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
@@ -5827,7 +5827,7 @@
 🔹 GM 55565480
 ✅ Подходит: GM · 55565480 (5636119)
 🔩 Номер детали: 55565480
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N55" s="7" t="inlineStr">
@@ -5927,7 +5927,7 @@
 🔹 Плотнее прилегают и служат дольше аналогов
 🔹 Комплект на 2 штока
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
@@ -6027,7 +6027,7 @@
 🔹 Новые, с завода
 🔹 Отправка в день заказа
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
@@ -6133,7 +6133,7 @@
 🔹 То же с оригинальными пыльниками VW
 🔹 Плита + фильтр + 2 оригинальных сальника VW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
@@ -6229,7 +6229,7 @@
 🔹 Защита от загрязнений
 🔹 Против подтёков масла
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
@@ -6325,7 +6325,7 @@
 🔹 Меняются парой со штоками
 🔹 Новые втулки без новых штоков проблему не решают
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
@@ -6426,7 +6426,7 @@
 🔹 Резиновое кольцо в комплекте
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ500 (0BH)
 🔩 Номер детали: 0BH325183B
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
@@ -6523,7 +6523,7 @@
 🔹 Номер детали 0AM325025Q
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325025Q
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
@@ -6619,7 +6619,7 @@
 🔹 4 штатных сальника
 🔹 4 усиленных алюминиевых сальника
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
@@ -6715,7 +6715,7 @@
 🔹 Сепараторная пластина — отдельно (0AM325467J)
 🔹 Для 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
@@ -6817,7 +6817,7 @@
 🔹 Предотвращают потерю давления
 🔹 Комплект 2 кольца или по одному
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
@@ -6919,7 +6919,7 @@
 🔹 Усиленные детали (гидроплита, штоки, поршни) — утолщённые стенки, дополнительные резинки, рассчитаны на больший ресурс
 🔹 Оригинал VAG (сальники, пыльники) — заводское качество и плотная посадка
 Как правило, в ремкомплектах лучше сочетать: усиленные детали там, где нагрузка выше, и оригинальные уплотнения.
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -7006,7 +7006,7 @@
 🔹 Всё для обновления обоих штоков
 🔹 Новые материалы, отличное качество
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
@@ -7106,7 +7106,7 @@
 🔹 Улучшенный отвод тепла
 🔹 Снижает температуру масла
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ500 (0BH)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
@@ -7209,7 +7209,7 @@
 🔹 Планка 1 шт или комплект 2 шт
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325477AE
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
@@ -7309,7 +7309,7 @@
 🔹 Вариант с обычными деталями
 🔹 Вариант с оригинальными (VAG) пыльниками и сальниками
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
@@ -7405,7 +7405,7 @@
 🔹 Предотвращает подтёки масла
 🔹 Новая, отправка в день заказа
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Ozon · WB · Авито · Сайт</t>
+          <t>Ozon · WB · Маркет · Сайт</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
@@ -7484,7 +7484,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>Единый слайд: логотипы площадок (Ozon, WB, Авито, сайт) + QR/ссылки
+          <t>Единый слайд: логотипы площадок (Ozon, WB, Яндекс Маркет, сайт) + QR/ссылки
 Заголовок и подзаголовок как в таблице</t>
         </is>
       </c>
@@ -7498,10 +7498,10 @@
           <t>Где купить запчасти Leo.Parts? 🛒
 • Ozon
 • Wildberries
-• Авито
+• Яндекс Маркет
 • Наш сайт
-Все ссылки — в шапке профиля. На сайте и на Авито цены ниже, чем на маркетплейсах 😉
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+Все ссылки — в шапке профиля. На сайте цены ниже, чем на маркетплейсах 😉
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N72" s="4" t="inlineStr">
@@ -7590,7 +7590,7 @@
 🔹 Точная и стабильная работа
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325066AC
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
@@ -7687,7 +7687,7 @@
 🔹 Отличное качество
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325025R
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
@@ -7783,7 +7783,7 @@
 🔹 Подходит под короткий и длинный шток
 🔹 Комплект: сальник, пыльник, крышка
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N75" s="7" t="inlineStr">
@@ -7879,7 +7879,7 @@
 🔹 Для тех, у кого треснул или потерян корпус
 🔹 Volkswagen, Škoda, Audi, Seat, Porsche
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat, Porsche · DSG7 DQ500 (0BH)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N76" s="7" t="inlineStr">
@@ -7980,7 +7980,7 @@
 🔹 Уплотнения для сборки после ремонта
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325025M
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N77" s="7" t="inlineStr">
@@ -8082,7 +8082,7 @@
 🔹 Уплотнение электромотора гидроблока
 🔹 Уплотнение насоса гидроблока
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
@@ -8182,7 +8182,7 @@
 🔹 Выходной вал — вторичный вал коробки
 🔹 Меняются при течи масла в этой зоне
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N79" s="7" t="inlineStr">
@@ -8280,7 +8280,7 @@
           <t>Что именно лежит в ремкомплекте мехатроника DQ200? Разбираем по слайдам 👉
 В зависимости от комплектации это прокладки и уплотнения, гидроплита, сальники, пыльники, крышки штоков. Есть полные комплекты и точечные — под конкретную поломку.
 В каталоге — ссылки в шапке профиля 📦
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -8368,7 +8368,7 @@
 🔹 Обратный клапан масляного фильтра
 🔹 Комплектом выгоднее, чем по отдельности
 ✅ Подходит: Двигатели VAG EA888 Gen3 · 1.8 TSI и 2.0 TSI
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N81" s="7" t="inlineStr">
@@ -8469,7 +8469,7 @@
 🔹 Есть восстановленный оригинал VAG
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325587E
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N82" s="7" t="inlineStr">
@@ -8569,7 +8569,7 @@
 🔹 2 пыльника и 2 крышки
 🔹 Для мехатроников 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N83" s="7" t="inlineStr">
@@ -8669,7 +8669,7 @@
 🔹 Комплект на 2 штока полностью
 🔹 Для мехатроников 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N84" s="7" t="inlineStr">
@@ -8771,7 +8771,7 @@
 🔹 2 пыльника + 2 сальника штоков
 🔹 Есть вариант с оригинальными (VAG) пыльниками и сальниками
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N85" s="7" t="inlineStr">
@@ -8874,7 +8874,7 @@
 🔹 Набор: 4 длинных + 3 коротких
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 01X301127C, WHT001922
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N86" s="7" t="inlineStr">
@@ -8970,7 +8970,7 @@
 🔹 Поэтому подшипник один
 🔹 Для DQ200 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
@@ -9070,7 +9070,7 @@
 🔹 Защищает соленоиды от загрязнений
 🔹 Аналог 123014AF и оригинальный вариант
 ✅ Подходит: Audi Q5, A4, A5 и другие · DSG7 0B5 (DL501) / DQ500 (0BH)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N88" s="7" t="inlineStr">
@@ -9166,7 +9166,7 @@
 🔹 Всегда в наличии
 🔹 Для мехатроника 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N89" s="7" t="inlineStr">
@@ -9263,7 +9263,7 @@
 🔹 Для мехатроника DQ200 0AM / 0CW
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325025L
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N90" s="7" t="inlineStr">
@@ -9364,7 +9364,7 @@
 🔹 Одна клипса или комплект 2 шт
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat · DSG7 DQ200 (0AM / 0CW)
 🔩 Номер детали: 0AM325025P
-📩 Заказать: Ozon, Wildberries, Авито и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
+📩 Заказать: Ozon, Wildberries, Яндекс Маркет и наш сайт — ссылки в шапке профиля. Вопросы по подбору — в сообщения.</t>
         </is>
       </c>
       <c r="N91" s="7" t="inlineStr">
@@ -9459,7 +9459,7 @@
         <is>
           <t>Штатный корпус масляного фильтра на DSG — пластиковый, и это слабое место 🔧
 Алюминиевый корпус прочнее и лучше отводит тепло: масло в коробке меньше греется. Для DSG6 DQ250 и DSG7 DQ500 у нас есть алюминиевые корпуса, а также наборы с фильтром.
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N92" s="4" t="inlineStr">
@@ -9546,7 +9546,7 @@
           <t>Новый шток в старую втулку? Так не работает 🙅
 Новые втулки без новых штоков не устраняют проблему, и наоборот. Меняйте их парой, а для герметичности добавьте прокладки-кольца втулки.
 Готовые комплекты «2 штока + 2 втулки» — в каталоге.
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N93" s="4" t="inlineStr">
@@ -9633,7 +9633,7 @@
         <is>
           <t>DSG6 DQ250 (код 02E) — другая коробка, чем DQ200. Мокрое сцепление, 6 ступеней 🔧
 Для неё у нас есть масляные фильтры, алюминиевые корпуса фильтра и готовый мехатроник в сборе с электронной платой.
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N94" s="4" t="inlineStr">
@@ -9720,7 +9720,7 @@
         <is>
           <t>Двигатели EA888 Gen3 (1.8 и 2.0 TSI) — слабое место: штатный пластиковый корпус масляного фильтра 🔧
 Алюминиевый корпус заменяет пластиковый. Есть корпус отдельно, обратный клапан отдельно и комплект: выгоднее, чем по частям.
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -9806,7 +9806,7 @@
         <is>
           <t>Гидроблок вариатора управляет давлением масла в CVT и от него зависит корректная работа трансмиссии ⚙️
 Применяется в вариаторах Nissan, Renault, Mitsubishi. В каталоге — гидроблок JF015E (RE0F11A) 1.8 л.
-📩 Ссылки на Ozon, Wildberries, Авито и сайт — в шапке профиля.</t>
+📩 Ссылки на Ozon, Wildberries, Яндекс Маркет и сайт — в шапке профиля.</t>
         </is>
       </c>
       <c r="N96" s="4" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Слайд 1: обложка с заголовком. Дальше — по слайду на вариант товара (см. колонку «Состав слайдов»). Последний слайд: «Где купить: Ozon · WB · Авито · сайт» без цен.</t>
+          <t>Слайд 1: обложка с заголовком. Дальше — по слайду на вариант товара (см. колонку «Состав слайдов»). Последний слайд: «Где купить: Ozon · WB · Маркет · сайт» без цен.</t>
         </is>
       </c>
     </row>
